--- a/research/traditional_assets/database/data/colombia/colombia_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_retail_automotive.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09464495437553051</v>
+        <v>0.09434294703521617</v>
       </c>
       <c r="C2">
-        <v>1306.259409561752</v>
+        <v>1294.886278538846</v>
       </c>
       <c r="D2">
-        <v>1049.859409561752</v>
+        <v>1052.760278538846</v>
       </c>
       <c r="E2">
-        <v>-953.8</v>
+        <v>-939.526</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14.274</v>
       </c>
       <c r="G2">
         <v>256.4</v>
@@ -1451,28 +1451,28 @@
         <v>394.925</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7179822</v>
       </c>
       <c r="N2">
-        <v>394.925</v>
+        <v>394.2070178</v>
       </c>
       <c r="O2">
-        <v>138.22375</v>
+        <v>137.97245623</v>
       </c>
       <c r="P2">
-        <v>256.70125</v>
+        <v>256.23456157</v>
       </c>
       <c r="Q2">
-        <v>298.9012499999999</v>
+        <v>298.43456157</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09464495437553051</v>
+        <v>0.09496565357092543</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307608</v>
+        <v>0.7154201659838416</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>550.0484552402552</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09434294703521617</v>
+        <v>0.09404093969490179</v>
       </c>
       <c r="C3">
-        <v>1294.886278538846</v>
+        <v>1283.529222729038</v>
       </c>
       <c r="D3">
-        <v>1052.760278538846</v>
+        <v>1055.677222729038</v>
       </c>
       <c r="E3">
-        <v>-939.526</v>
+        <v>-925.252</v>
       </c>
       <c r="F3">
-        <v>14.274</v>
+        <v>28.548</v>
       </c>
       <c r="G3">
         <v>256.4</v>
@@ -1533,28 +1533,28 @@
         <v>394.925</v>
       </c>
       <c r="M3">
-        <v>0.7179822</v>
+        <v>1.4359644</v>
       </c>
       <c r="N3">
-        <v>394.2070178</v>
+        <v>393.4890356</v>
       </c>
       <c r="O3">
-        <v>137.97245623</v>
+        <v>137.72116246</v>
       </c>
       <c r="P3">
-        <v>256.23456157</v>
+        <v>255.76787314</v>
       </c>
       <c r="Q3">
-        <v>298.43456157</v>
+        <v>297.9678731399999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09496565357092543</v>
+        <v>0.09529289764785898</v>
       </c>
       <c r="T3">
-        <v>0.7154201659838416</v>
+        <v>0.7201819660380055</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>550.0484552402552</v>
+        <v>275.0242276201276</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09404093969490179</v>
+        <v>0.09373893235458745</v>
       </c>
       <c r="C4">
-        <v>1283.529222729038</v>
+        <v>1272.188376125176</v>
       </c>
       <c r="D4">
-        <v>1055.677222729038</v>
+        <v>1058.610376125176</v>
       </c>
       <c r="E4">
-        <v>-925.252</v>
+        <v>-910.978</v>
       </c>
       <c r="F4">
-        <v>28.548</v>
+        <v>42.822</v>
       </c>
       <c r="G4">
         <v>256.4</v>
@@ -1615,28 +1615,28 @@
         <v>394.925</v>
       </c>
       <c r="M4">
-        <v>1.4359644</v>
+        <v>2.1539466</v>
       </c>
       <c r="N4">
-        <v>393.4890356</v>
+        <v>392.7710534</v>
       </c>
       <c r="O4">
-        <v>137.72116246</v>
+        <v>137.46986869</v>
       </c>
       <c r="P4">
-        <v>255.76787314</v>
+        <v>255.30118471</v>
       </c>
       <c r="Q4">
-        <v>297.9678731399999</v>
+        <v>297.50118471</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09529289764785898</v>
+        <v>0.09562688902534788</v>
       </c>
       <c r="T4">
-        <v>0.7201819660380055</v>
+        <v>0.7250419475365852</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>275.0242276201276</v>
+        <v>183.3494850800851</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09373893235458745</v>
+        <v>0.09343692501427307</v>
       </c>
       <c r="C5">
-        <v>1272.188376125176</v>
+        <v>1260.86387421343</v>
       </c>
       <c r="D5">
-        <v>1058.610376125176</v>
+        <v>1061.55987421343</v>
       </c>
       <c r="E5">
-        <v>-910.978</v>
+        <v>-896.704</v>
       </c>
       <c r="F5">
-        <v>42.822</v>
+        <v>57.096</v>
       </c>
       <c r="G5">
         <v>256.4</v>
@@ -1697,28 +1697,28 @@
         <v>394.925</v>
       </c>
       <c r="M5">
-        <v>2.1539466</v>
+        <v>2.8719288</v>
       </c>
       <c r="N5">
-        <v>392.7710534</v>
+        <v>392.0530712</v>
       </c>
       <c r="O5">
-        <v>137.46986869</v>
+        <v>137.21857492</v>
       </c>
       <c r="P5">
-        <v>255.30118471</v>
+        <v>254.83449628</v>
       </c>
       <c r="Q5">
-        <v>297.50118471</v>
+        <v>297.03449628</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09562688902534788</v>
+        <v>0.09596783855653446</v>
       </c>
       <c r="T5">
-        <v>0.7250419475365852</v>
+        <v>0.7300031786497189</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>183.3494850800851</v>
+        <v>137.5121138100638</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09343692501427307</v>
+        <v>0.09313491767395873</v>
       </c>
       <c r="C6">
-        <v>1260.86387421343</v>
+        <v>1249.555853994155</v>
       </c>
       <c r="D6">
-        <v>1061.55987421343</v>
+        <v>1064.525853994155</v>
       </c>
       <c r="E6">
-        <v>-896.704</v>
+        <v>-882.4299999999999</v>
       </c>
       <c r="F6">
-        <v>57.096</v>
+        <v>71.37</v>
       </c>
       <c r="G6">
         <v>256.4</v>
@@ -1779,28 +1779,28 @@
         <v>394.925</v>
       </c>
       <c r="M6">
-        <v>2.8719288</v>
+        <v>3.589911</v>
       </c>
       <c r="N6">
-        <v>392.0530712</v>
+        <v>391.335089</v>
       </c>
       <c r="O6">
-        <v>137.21857492</v>
+        <v>136.96728115</v>
       </c>
       <c r="P6">
-        <v>254.83449628</v>
+        <v>254.36780785</v>
       </c>
       <c r="Q6">
-        <v>297.03449628</v>
+        <v>296.56780785</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09596783855653446</v>
+        <v>0.09631596597258814</v>
       </c>
       <c r="T6">
-        <v>0.7300031786497189</v>
+        <v>0.7350688567336552</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>137.5121138100638</v>
+        <v>110.0096910480511</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09313491767395873</v>
+        <v>0.09283291033364437</v>
       </c>
       <c r="C7">
-        <v>1249.555853994155</v>
+        <v>1238.264454003102</v>
       </c>
       <c r="D7">
-        <v>1064.525853994155</v>
+        <v>1067.508454003102</v>
       </c>
       <c r="E7">
-        <v>-882.4299999999999</v>
+        <v>-868.1559999999999</v>
       </c>
       <c r="F7">
-        <v>71.37</v>
+        <v>85.64400000000001</v>
       </c>
       <c r="G7">
         <v>256.4</v>
@@ -1861,28 +1861,28 @@
         <v>394.925</v>
       </c>
       <c r="M7">
-        <v>3.589911</v>
+        <v>4.3078932</v>
       </c>
       <c r="N7">
-        <v>391.335089</v>
+        <v>390.6171067999999</v>
       </c>
       <c r="O7">
-        <v>136.96728115</v>
+        <v>136.71598738</v>
       </c>
       <c r="P7">
-        <v>254.36780785</v>
+        <v>253.90111942</v>
       </c>
       <c r="Q7">
-        <v>296.56780785</v>
+        <v>296.1011194199999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09631596597258814</v>
+        <v>0.09667150035494082</v>
       </c>
       <c r="T7">
-        <v>0.7350688567336552</v>
+        <v>0.7402423152023562</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>110.0096910480511</v>
+        <v>91.67474254004253</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09283291033364437</v>
+        <v>0.09253090299333001</v>
       </c>
       <c r="C8">
-        <v>1238.264454003102</v>
+        <v>1226.989814332986</v>
       </c>
       <c r="D8">
-        <v>1067.508454003102</v>
+        <v>1070.507814332986</v>
       </c>
       <c r="E8">
-        <v>-868.1559999999999</v>
+        <v>-853.8819999999999</v>
       </c>
       <c r="F8">
-        <v>85.64400000000001</v>
+        <v>99.91799999999999</v>
       </c>
       <c r="G8">
         <v>256.4</v>
@@ -1943,28 +1943,28 @@
         <v>394.925</v>
       </c>
       <c r="M8">
-        <v>4.3078932</v>
+        <v>5.025875399999999</v>
       </c>
       <c r="N8">
-        <v>390.6171067999999</v>
+        <v>389.8991245999999</v>
       </c>
       <c r="O8">
-        <v>136.71598738</v>
+        <v>136.46469361</v>
       </c>
       <c r="P8">
-        <v>253.90111942</v>
+        <v>253.43443099</v>
       </c>
       <c r="Q8">
-        <v>296.1011194199999</v>
+        <v>295.6344309899999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09667150035494082</v>
+        <v>0.09703468063798926</v>
       </c>
       <c r="T8">
-        <v>0.7402423152023562</v>
+        <v>0.745527030842427</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>91.67474254004253</v>
+        <v>78.57835074860789</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09253090299333</v>
+        <v>0.09222889565301566</v>
       </c>
       <c r="C9">
-        <v>1226.989814332986</v>
+        <v>1215.732076655427</v>
       </c>
       <c r="D9">
-        <v>1070.507814332987</v>
+        <v>1073.524076655427</v>
       </c>
       <c r="E9">
-        <v>-853.8819999999999</v>
+        <v>-839.6079999999999</v>
       </c>
       <c r="F9">
-        <v>99.91800000000002</v>
+        <v>114.192</v>
       </c>
       <c r="G9">
         <v>256.4</v>
@@ -2025,28 +2025,28 @@
         <v>394.925</v>
       </c>
       <c r="M9">
-        <v>5.025875400000001</v>
+        <v>5.7438576</v>
       </c>
       <c r="N9">
-        <v>389.8991245999999</v>
+        <v>389.1811423999999</v>
       </c>
       <c r="O9">
-        <v>136.46469361</v>
+        <v>136.21339984</v>
       </c>
       <c r="P9">
-        <v>253.43443099</v>
+        <v>252.96774256</v>
       </c>
       <c r="Q9">
-        <v>295.6344309899999</v>
+        <v>295.16774256</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09703468063798926</v>
+        <v>0.09740575614458225</v>
       </c>
       <c r="T9">
-        <v>0.745527030842427</v>
+        <v>0.7509266316051081</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>78.57835074860786</v>
+        <v>68.7560569050319</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09222889565301566</v>
+        <v>0.09192688831270131</v>
       </c>
       <c r="C10">
-        <v>1215.732076655427</v>
+        <v>1204.491384243248</v>
       </c>
       <c r="D10">
-        <v>1073.524076655427</v>
+        <v>1076.557384243248</v>
       </c>
       <c r="E10">
-        <v>-839.6079999999999</v>
+        <v>-825.3339999999999</v>
       </c>
       <c r="F10">
-        <v>114.192</v>
+        <v>128.466</v>
       </c>
       <c r="G10">
         <v>256.4</v>
@@ -2107,28 +2107,28 @@
         <v>394.925</v>
       </c>
       <c r="M10">
-        <v>5.7438576</v>
+        <v>6.4618398</v>
       </c>
       <c r="N10">
-        <v>389.1811423999999</v>
+        <v>388.4631601999999</v>
       </c>
       <c r="O10">
-        <v>136.21339984</v>
+        <v>135.96210607</v>
       </c>
       <c r="P10">
-        <v>252.96774256</v>
+        <v>252.50105413</v>
       </c>
       <c r="Q10">
-        <v>295.16774256</v>
+        <v>294.70105413</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09740575614458225</v>
+        <v>0.09778498715681462</v>
       </c>
       <c r="T10">
-        <v>0.7509266316051081</v>
+        <v>0.756444904912024</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>68.7560569050319</v>
+        <v>61.11649502669502</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09192688831270131</v>
+        <v>0.09162488097238694</v>
       </c>
       <c r="C11">
-        <v>1204.491384243248</v>
+        <v>1193.267881993167</v>
       </c>
       <c r="D11">
-        <v>1076.557384243248</v>
+        <v>1079.607881993167</v>
       </c>
       <c r="E11">
-        <v>-825.3339999999999</v>
+        <v>-811.0599999999999</v>
       </c>
       <c r="F11">
-        <v>128.466</v>
+        <v>142.74</v>
       </c>
       <c r="G11">
         <v>256.4</v>
@@ -2189,28 +2189,28 @@
         <v>394.925</v>
       </c>
       <c r="M11">
-        <v>6.4618398</v>
+        <v>7.179822</v>
       </c>
       <c r="N11">
-        <v>388.4631601999999</v>
+        <v>387.745178</v>
       </c>
       <c r="O11">
-        <v>135.96210607</v>
+        <v>135.7108123</v>
       </c>
       <c r="P11">
-        <v>252.50105413</v>
+        <v>252.0343657</v>
       </c>
       <c r="Q11">
-        <v>294.70105413</v>
+        <v>294.2343657</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09778498715681462</v>
+        <v>0.09817264552487438</v>
       </c>
       <c r="T11">
-        <v>0.756444904912024</v>
+        <v>0.762085806514649</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>61.11649502669502</v>
+        <v>55.00484552402552</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09162488097238694</v>
+        <v>0.0913228736320726</v>
       </c>
       <c r="C12">
-        <v>1193.267881993167</v>
+        <v>1182.061716448867</v>
       </c>
       <c r="D12">
-        <v>1079.607881993167</v>
+        <v>1082.675716448867</v>
       </c>
       <c r="E12">
-        <v>-811.0599999999999</v>
+        <v>-796.7859999999999</v>
       </c>
       <c r="F12">
-        <v>142.74</v>
+        <v>157.014</v>
       </c>
       <c r="G12">
         <v>256.4</v>
@@ -2271,28 +2271,28 @@
         <v>394.925</v>
       </c>
       <c r="M12">
-        <v>7.179822</v>
+        <v>7.8978042</v>
       </c>
       <c r="N12">
-        <v>387.745178</v>
+        <v>387.0271958</v>
       </c>
       <c r="O12">
-        <v>135.7108123</v>
+        <v>135.45951853</v>
       </c>
       <c r="P12">
-        <v>252.0343657</v>
+        <v>251.56767727</v>
       </c>
       <c r="Q12">
-        <v>294.2343657</v>
+        <v>293.76767727</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09817264552487438</v>
+        <v>0.0985690153169355</v>
       </c>
       <c r="T12">
-        <v>0.762085806514649</v>
+        <v>0.7678534699510411</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>55.00484552402552</v>
+        <v>50.00440502184138</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0913228736320726</v>
+        <v>0.09102086629175823</v>
       </c>
       <c r="C13">
-        <v>1182.061716448867</v>
+        <v>1170.873035824462</v>
       </c>
       <c r="D13">
-        <v>1082.675716448867</v>
+        <v>1085.761035824462</v>
       </c>
       <c r="E13">
-        <v>-796.7859999999999</v>
+        <v>-782.5119999999999</v>
       </c>
       <c r="F13">
-        <v>157.014</v>
+        <v>171.288</v>
       </c>
       <c r="G13">
         <v>256.4</v>
@@ -2353,28 +2353,28 @@
         <v>394.925</v>
       </c>
       <c r="M13">
-        <v>7.8978042</v>
+        <v>8.615786399999999</v>
       </c>
       <c r="N13">
-        <v>387.0271958</v>
+        <v>386.3092136</v>
       </c>
       <c r="O13">
-        <v>135.45951853</v>
+        <v>135.20822476</v>
       </c>
       <c r="P13">
-        <v>251.56767727</v>
+        <v>251.10098884</v>
       </c>
       <c r="Q13">
-        <v>293.76767727</v>
+        <v>293.3009888399999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0985690153169355</v>
+        <v>0.09897439351336162</v>
       </c>
       <c r="T13">
-        <v>0.7678534699510411</v>
+        <v>0.7737522166473509</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>50.00440502184138</v>
+        <v>45.83737127002127</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09102086629175823</v>
+        <v>0.09071885895144387</v>
       </c>
       <c r="C14">
-        <v>1170.873035824462</v>
+        <v>1159.701990028369</v>
       </c>
       <c r="D14">
-        <v>1085.761035824462</v>
+        <v>1088.863990028368</v>
       </c>
       <c r="E14">
-        <v>-782.5119999999999</v>
+        <v>-768.2379999999999</v>
       </c>
       <c r="F14">
-        <v>171.288</v>
+        <v>185.562</v>
       </c>
       <c r="G14">
         <v>256.4</v>
@@ -2435,28 +2435,28 @@
         <v>394.925</v>
       </c>
       <c r="M14">
-        <v>8.615786399999999</v>
+        <v>9.333768600000001</v>
       </c>
       <c r="N14">
-        <v>386.3092136</v>
+        <v>385.5912314</v>
       </c>
       <c r="O14">
-        <v>135.20822476</v>
+        <v>134.95693099</v>
       </c>
       <c r="P14">
-        <v>251.10098884</v>
+        <v>250.63430041</v>
       </c>
       <c r="Q14">
-        <v>293.3009888399999</v>
+        <v>292.83430041</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09897439351336162</v>
+        <v>0.09938909074878606</v>
       </c>
       <c r="T14">
-        <v>0.7737522166473509</v>
+        <v>0.7797865667159898</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>45.83737127002127</v>
+        <v>42.31141963386578</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09071885895144387</v>
+        <v>0.09041685161112953</v>
       </c>
       <c r="C15">
-        <v>1159.701990028369</v>
+        <v>1148.548730687583</v>
       </c>
       <c r="D15">
-        <v>1088.863990028368</v>
+        <v>1091.984730687583</v>
       </c>
       <c r="E15">
-        <v>-768.2379999999999</v>
+        <v>-753.9639999999999</v>
       </c>
       <c r="F15">
-        <v>185.562</v>
+        <v>199.836</v>
       </c>
       <c r="G15">
         <v>256.4</v>
@@ -2517,28 +2517,28 @@
         <v>394.925</v>
       </c>
       <c r="M15">
-        <v>9.333768600000001</v>
+        <v>10.0517508</v>
       </c>
       <c r="N15">
-        <v>385.5912314</v>
+        <v>384.8732492</v>
       </c>
       <c r="O15">
-        <v>134.95693099</v>
+        <v>134.70563722</v>
       </c>
       <c r="P15">
-        <v>250.63430041</v>
+        <v>250.16761198</v>
       </c>
       <c r="Q15">
-        <v>292.83430041</v>
+        <v>292.36761198</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09938909074878606</v>
+        <v>0.09981343210596456</v>
       </c>
       <c r="T15">
-        <v>0.7797865667159898</v>
+        <v>0.7859612505071553</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>42.31141963386578</v>
+        <v>39.28917537430394</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09041685161112953</v>
+        <v>0.09011484427081516</v>
       </c>
       <c r="C16">
-        <v>1148.548730687583</v>
+        <v>1137.413411172383</v>
       </c>
       <c r="D16">
-        <v>1091.984730687583</v>
+        <v>1095.123411172383</v>
       </c>
       <c r="E16">
-        <v>-753.9639999999999</v>
+        <v>-739.6899999999999</v>
       </c>
       <c r="F16">
-        <v>199.836</v>
+        <v>214.11</v>
       </c>
       <c r="G16">
         <v>256.4</v>
@@ -2599,28 +2599,28 @@
         <v>394.925</v>
       </c>
       <c r="M16">
-        <v>10.0517508</v>
+        <v>10.769733</v>
       </c>
       <c r="N16">
-        <v>384.8732492</v>
+        <v>384.155267</v>
       </c>
       <c r="O16">
-        <v>134.70563722</v>
+        <v>134.45434345</v>
       </c>
       <c r="P16">
-        <v>250.16761198</v>
+        <v>249.70092355</v>
       </c>
       <c r="Q16">
-        <v>292.36761198</v>
+        <v>291.90092355</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09981343210596456</v>
+        <v>0.1002477579656649</v>
       </c>
       <c r="T16">
-        <v>0.7859612505071553</v>
+        <v>0.7922812209757598</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>39.28917537430394</v>
+        <v>36.66989701601701</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09011484427081516</v>
+        <v>0.08981283693050081</v>
       </c>
       <c r="C17">
-        <v>1137.413411172383</v>
+        <v>1126.29618662145</v>
       </c>
       <c r="D17">
-        <v>1095.123411172383</v>
+        <v>1098.280186621451</v>
       </c>
       <c r="E17">
-        <v>-739.6899999999999</v>
+        <v>-725.4159999999999</v>
       </c>
       <c r="F17">
-        <v>214.11</v>
+        <v>228.384</v>
       </c>
       <c r="G17">
         <v>256.4</v>
@@ -2681,28 +2681,28 @@
         <v>394.925</v>
       </c>
       <c r="M17">
-        <v>10.769733</v>
+        <v>11.4877152</v>
       </c>
       <c r="N17">
-        <v>384.155267</v>
+        <v>383.4372847999999</v>
       </c>
       <c r="O17">
-        <v>134.45434345</v>
+        <v>134.20304968</v>
       </c>
       <c r="P17">
-        <v>249.70092355</v>
+        <v>249.23423512</v>
       </c>
       <c r="Q17">
-        <v>291.90092355</v>
+        <v>291.4342351199999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1002477579656649</v>
+        <v>0.1006924249172629</v>
       </c>
       <c r="T17">
-        <v>0.7922812209757598</v>
+        <v>0.7987516669317121</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>36.66989701601701</v>
+        <v>34.37802845251595</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08981283693050081</v>
+        <v>0.08951082959018646</v>
       </c>
       <c r="C18">
-        <v>1126.29618662145</v>
+        <v>1115.197213967435</v>
       </c>
       <c r="D18">
-        <v>1098.280186621451</v>
+        <v>1101.455213967435</v>
       </c>
       <c r="E18">
-        <v>-725.4159999999999</v>
+        <v>-711.1419999999999</v>
       </c>
       <c r="F18">
-        <v>228.384</v>
+        <v>242.658</v>
       </c>
       <c r="G18">
         <v>256.4</v>
@@ -2763,28 +2763,28 @@
         <v>394.925</v>
       </c>
       <c r="M18">
-        <v>11.4877152</v>
+        <v>12.2056974</v>
       </c>
       <c r="N18">
-        <v>383.4372847999999</v>
+        <v>382.7193025999999</v>
       </c>
       <c r="O18">
-        <v>134.20304968</v>
+        <v>133.95175591</v>
       </c>
       <c r="P18">
-        <v>249.23423512</v>
+        <v>248.76754669</v>
       </c>
       <c r="Q18">
-        <v>291.4342351199999</v>
+        <v>290.9675466899999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1006924249172629</v>
+        <v>0.1011478067351644</v>
       </c>
       <c r="T18">
-        <v>0.7987516669317121</v>
+        <v>0.8053780272480489</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>34.37802845251595</v>
+        <v>32.35579148472089</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08951082959018646</v>
+        <v>0.08920882224987209</v>
       </c>
       <c r="C19">
-        <v>1115.197213967435</v>
+        <v>1104.116651962958</v>
       </c>
       <c r="D19">
-        <v>1101.455213967435</v>
+        <v>1104.648651962958</v>
       </c>
       <c r="E19">
-        <v>-711.1419999999999</v>
+        <v>-696.8679999999999</v>
       </c>
       <c r="F19">
-        <v>242.658</v>
+        <v>256.9320000000001</v>
       </c>
       <c r="G19">
         <v>256.4</v>
@@ -2845,28 +2845,28 @@
         <v>394.925</v>
       </c>
       <c r="M19">
-        <v>12.2056974</v>
+        <v>12.9236796</v>
       </c>
       <c r="N19">
-        <v>382.7193025999999</v>
+        <v>382.0013203999999</v>
       </c>
       <c r="O19">
-        <v>133.95175591</v>
+        <v>133.70046214</v>
       </c>
       <c r="P19">
-        <v>248.76754669</v>
+        <v>248.30085826</v>
       </c>
       <c r="Q19">
-        <v>290.9675466899999</v>
+        <v>290.50085826</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1011478067351644</v>
+        <v>0.1016142954266733</v>
       </c>
       <c r="T19">
-        <v>0.8053780272480489</v>
+        <v>0.8121660061086863</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>32.35579148472089</v>
+        <v>30.5582475133475</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08920882224987209</v>
+        <v>0.08890681490955774</v>
       </c>
       <c r="C20">
-        <v>1104.116651962958</v>
+        <v>1093.054661207074</v>
       </c>
       <c r="D20">
-        <v>1104.648651962958</v>
+        <v>1107.860661207075</v>
       </c>
       <c r="E20">
-        <v>-696.8679999999999</v>
+        <v>-682.5939999999999</v>
       </c>
       <c r="F20">
-        <v>256.932</v>
+        <v>271.206</v>
       </c>
       <c r="G20">
         <v>256.4</v>
@@ -2927,28 +2927,28 @@
         <v>394.925</v>
       </c>
       <c r="M20">
-        <v>12.9236796</v>
+        <v>13.6416618</v>
       </c>
       <c r="N20">
-        <v>382.0013203999999</v>
+        <v>381.2833381999999</v>
       </c>
       <c r="O20">
-        <v>133.70046214</v>
+        <v>133.44916837</v>
       </c>
       <c r="P20">
-        <v>248.30085826</v>
+        <v>247.83416983</v>
       </c>
       <c r="Q20">
-        <v>290.50085826</v>
+        <v>290.03416983</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1016142954266733</v>
+        <v>0.1020923023574787</v>
       </c>
       <c r="T20">
-        <v>0.8121660061086863</v>
+        <v>0.8191215893856361</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>30.55824751334751</v>
+        <v>28.94991869685554</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08890681490955774</v>
+        <v>0.08860480756924338</v>
       </c>
       <c r="C21">
-        <v>1093.054661207074</v>
+        <v>1082.011404172195</v>
       </c>
       <c r="D21">
-        <v>1107.860661207075</v>
+        <v>1111.091404172196</v>
       </c>
       <c r="E21">
-        <v>-682.5939999999999</v>
+        <v>-668.3199999999999</v>
       </c>
       <c r="F21">
-        <v>271.206</v>
+        <v>285.48</v>
       </c>
       <c r="G21">
         <v>256.4</v>
@@ -3009,28 +3009,28 @@
         <v>394.925</v>
       </c>
       <c r="M21">
-        <v>13.6416618</v>
+        <v>14.359644</v>
       </c>
       <c r="N21">
-        <v>381.2833381999999</v>
+        <v>380.565356</v>
       </c>
       <c r="O21">
-        <v>133.44916837</v>
+        <v>133.1978746</v>
       </c>
       <c r="P21">
-        <v>247.83416983</v>
+        <v>247.3674814</v>
       </c>
       <c r="Q21">
-        <v>290.03416983</v>
+        <v>289.5674814</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1020923023574787</v>
+        <v>0.1025822594615542</v>
       </c>
       <c r="T21">
-        <v>0.8191215893856361</v>
+        <v>0.8262510622445094</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>28.94991869685554</v>
+        <v>27.50242276201276</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08860480756924338</v>
+        <v>0.08830280022892903</v>
       </c>
       <c r="C22">
-        <v>1082.011404172195</v>
+        <v>1070.987045231482</v>
       </c>
       <c r="D22">
-        <v>1111.091404172196</v>
+        <v>1114.341045231482</v>
       </c>
       <c r="E22">
-        <v>-668.3199999999999</v>
+        <v>-654.0459999999998</v>
       </c>
       <c r="F22">
-        <v>285.48</v>
+        <v>299.7540000000001</v>
       </c>
       <c r="G22">
         <v>256.4</v>
@@ -3091,28 +3091,28 @@
         <v>394.925</v>
       </c>
       <c r="M22">
-        <v>14.359644</v>
+        <v>15.0776262</v>
       </c>
       <c r="N22">
-        <v>380.565356</v>
+        <v>379.8473738</v>
       </c>
       <c r="O22">
-        <v>133.1978746</v>
+        <v>132.94658083</v>
       </c>
       <c r="P22">
-        <v>247.3674814</v>
+        <v>246.90079297</v>
       </c>
       <c r="Q22">
-        <v>289.5674814</v>
+        <v>289.1007929699999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1025822594615542</v>
+        <v>0.1030846205429481</v>
       </c>
       <c r="T22">
-        <v>0.8262510622445094</v>
+        <v>0.8335610280871517</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>27.50242276201276</v>
+        <v>26.19278358286929</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08830280022892903</v>
+        <v>0.08800079288861468</v>
       </c>
       <c r="C23">
-        <v>1070.987045231482</v>
+        <v>1059.981750686725</v>
       </c>
       <c r="D23">
-        <v>1114.341045231482</v>
+        <v>1117.609750686725</v>
       </c>
       <c r="E23">
-        <v>-654.0459999999999</v>
+        <v>-639.7719999999999</v>
       </c>
       <c r="F23">
-        <v>299.754</v>
+        <v>314.028</v>
       </c>
       <c r="G23">
         <v>256.4</v>
@@ -3173,28 +3173,28 @@
         <v>394.925</v>
       </c>
       <c r="M23">
-        <v>15.0776262</v>
+        <v>15.7956084</v>
       </c>
       <c r="N23">
-        <v>379.8473738</v>
+        <v>379.1293916</v>
       </c>
       <c r="O23">
-        <v>132.94658083</v>
+        <v>132.69528706</v>
       </c>
       <c r="P23">
-        <v>246.90079297</v>
+        <v>246.43410454</v>
       </c>
       <c r="Q23">
-        <v>289.1007929699999</v>
+        <v>288.63410454</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1030846205429481</v>
+        <v>0.1035998626777111</v>
       </c>
       <c r="T23">
-        <v>0.8335610280871517</v>
+        <v>0.8410584289514003</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>26.19278358286929</v>
+        <v>25.00220251092069</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08800079288861468</v>
+        <v>0.08769878554830031</v>
       </c>
       <c r="C24">
-        <v>1059.981750686725</v>
+        <v>1048.995688796711</v>
       </c>
       <c r="D24">
-        <v>1117.609750686725</v>
+        <v>1120.897688796711</v>
       </c>
       <c r="E24">
-        <v>-639.7719999999999</v>
+        <v>-625.4979999999999</v>
       </c>
       <c r="F24">
-        <v>314.028</v>
+        <v>328.302</v>
       </c>
       <c r="G24">
         <v>256.4</v>
@@ -3255,28 +3255,28 @@
         <v>394.925</v>
       </c>
       <c r="M24">
-        <v>15.7956084</v>
+        <v>16.5135906</v>
       </c>
       <c r="N24">
-        <v>379.1293916</v>
+        <v>378.4114094</v>
       </c>
       <c r="O24">
-        <v>132.69528706</v>
+        <v>132.44399329</v>
       </c>
       <c r="P24">
-        <v>246.43410454</v>
+        <v>245.96741611</v>
       </c>
       <c r="Q24">
-        <v>288.63410454</v>
+        <v>288.16741611</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1035998626777111</v>
+        <v>0.1041284877250653</v>
       </c>
       <c r="T24">
-        <v>0.8410584289514003</v>
+        <v>0.8487505675004344</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>25.00220251092069</v>
+        <v>23.91515022783718</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08769878554830031</v>
+        <v>0.08739677820798596</v>
       </c>
       <c r="C25">
-        <v>1048.995688796711</v>
+        <v>1038.029029806099</v>
       </c>
       <c r="D25">
-        <v>1120.897688796711</v>
+        <v>1124.205029806099</v>
       </c>
       <c r="E25">
-        <v>-625.4979999999999</v>
+        <v>-611.2239999999999</v>
       </c>
       <c r="F25">
-        <v>328.302</v>
+        <v>342.576</v>
       </c>
       <c r="G25">
         <v>256.4</v>
@@ -3337,28 +3337,28 @@
         <v>394.925</v>
       </c>
       <c r="M25">
-        <v>16.5135906</v>
+        <v>17.2315728</v>
       </c>
       <c r="N25">
-        <v>378.4114094</v>
+        <v>377.6934272</v>
       </c>
       <c r="O25">
-        <v>132.44399329</v>
+        <v>132.19269952</v>
       </c>
       <c r="P25">
-        <v>245.96741611</v>
+        <v>245.50072768</v>
       </c>
       <c r="Q25">
-        <v>288.16741611</v>
+        <v>287.70072768</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1041284877250653</v>
+        <v>0.1046710239578763</v>
       </c>
       <c r="T25">
-        <v>0.8487505675004344</v>
+        <v>0.8566451307481274</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>23.91515022783718</v>
+        <v>22.91868563501064</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08739677820798596</v>
+        <v>0.08709477086767162</v>
       </c>
       <c r="C26">
-        <v>1038.029029806099</v>
+        <v>1027.0819459748</v>
       </c>
       <c r="D26">
-        <v>1124.205029806099</v>
+        <v>1127.5319459748</v>
       </c>
       <c r="E26">
-        <v>-611.2239999999999</v>
+        <v>-596.9499999999999</v>
       </c>
       <c r="F26">
-        <v>342.576</v>
+        <v>356.85</v>
       </c>
       <c r="G26">
         <v>256.4</v>
@@ -3419,28 +3419,28 @@
         <v>394.925</v>
       </c>
       <c r="M26">
-        <v>17.2315728</v>
+        <v>17.949555</v>
       </c>
       <c r="N26">
-        <v>377.6934272</v>
+        <v>376.975445</v>
       </c>
       <c r="O26">
-        <v>132.19269952</v>
+        <v>131.94140575</v>
       </c>
       <c r="P26">
-        <v>245.50072768</v>
+        <v>245.03403925</v>
       </c>
       <c r="Q26">
-        <v>287.70072768</v>
+        <v>287.23403925</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1046710239578763</v>
+        <v>0.1052280278235621</v>
       </c>
       <c r="T26">
-        <v>0.8566451307481274</v>
+        <v>0.8647502156824257</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>22.91868563501064</v>
+        <v>22.00193820961021</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08709477086767162</v>
+        <v>0.08679276352735724</v>
       </c>
       <c r="C27">
-        <v>1027.0819459748</v>
+        <v>1016.154611607888</v>
       </c>
       <c r="D27">
-        <v>1127.5319459748</v>
+        <v>1130.878611607888</v>
       </c>
       <c r="E27">
-        <v>-596.9499999999999</v>
+        <v>-582.6759999999999</v>
       </c>
       <c r="F27">
-        <v>356.85</v>
+        <v>371.124</v>
       </c>
       <c r="G27">
         <v>256.4</v>
@@ -3501,28 +3501,28 @@
         <v>394.925</v>
       </c>
       <c r="M27">
-        <v>17.949555</v>
+        <v>18.6675372</v>
       </c>
       <c r="N27">
-        <v>376.975445</v>
+        <v>376.2574627999999</v>
       </c>
       <c r="O27">
-        <v>131.94140575</v>
+        <v>131.69011198</v>
       </c>
       <c r="P27">
-        <v>245.03403925</v>
+        <v>244.56735082</v>
       </c>
       <c r="Q27">
-        <v>287.23403925</v>
+        <v>286.7673508199999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1052280278235621</v>
+        <v>0.1058000858477801</v>
       </c>
       <c r="T27">
-        <v>0.8647502156824257</v>
+        <v>0.8730743569662993</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>22.00193820961021</v>
+        <v>21.15570981693289</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08679276352735724</v>
+        <v>0.0864907561870429</v>
       </c>
       <c r="C28">
-        <v>1016.154611607888</v>
+        <v>1005.24720308604</v>
       </c>
       <c r="D28">
-        <v>1130.878611607888</v>
+        <v>1134.24520308604</v>
       </c>
       <c r="E28">
-        <v>-582.6759999999999</v>
+        <v>-568.4019999999999</v>
       </c>
       <c r="F28">
-        <v>371.124</v>
+        <v>385.398</v>
       </c>
       <c r="G28">
         <v>256.4</v>
@@ -3583,28 +3583,28 @@
         <v>394.925</v>
       </c>
       <c r="M28">
-        <v>18.6675372</v>
+        <v>19.3855194</v>
       </c>
       <c r="N28">
-        <v>376.2574627999999</v>
+        <v>375.5394805999999</v>
       </c>
       <c r="O28">
-        <v>131.69011198</v>
+        <v>131.43881821</v>
       </c>
       <c r="P28">
-        <v>244.56735082</v>
+        <v>244.10066239</v>
       </c>
       <c r="Q28">
-        <v>286.7673508199999</v>
+        <v>286.30066239</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1058000858477801</v>
+        <v>0.1063878166945793</v>
       </c>
       <c r="T28">
-        <v>0.8730743569662993</v>
+        <v>0.8816265569154849</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>21.15570981693289</v>
+        <v>20.37216500889834</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0864907561870429</v>
+        <v>0.08618874884672852</v>
       </c>
       <c r="C29">
-        <v>1005.24720308604</v>
+        <v>994.3598988965241</v>
       </c>
       <c r="D29">
-        <v>1134.24520308604</v>
+        <v>1137.631898896524</v>
       </c>
       <c r="E29">
-        <v>-568.4019999999999</v>
+        <v>-554.1279999999999</v>
       </c>
       <c r="F29">
-        <v>385.398</v>
+        <v>399.6720000000001</v>
       </c>
       <c r="G29">
         <v>256.4</v>
@@ -3665,28 +3665,28 @@
         <v>394.925</v>
       </c>
       <c r="M29">
-        <v>19.3855194</v>
+        <v>20.1035016</v>
       </c>
       <c r="N29">
-        <v>375.5394805999999</v>
+        <v>374.8214983999999</v>
       </c>
       <c r="O29">
-        <v>131.43881821</v>
+        <v>131.18752444</v>
       </c>
       <c r="P29">
-        <v>244.10066239</v>
+        <v>243.63397396</v>
       </c>
       <c r="Q29">
-        <v>286.30066239</v>
+        <v>285.83397396</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1063878166945793</v>
+        <v>0.1069918733982341</v>
       </c>
       <c r="T29">
-        <v>0.8816265569154849</v>
+        <v>0.8904163179743697</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>20.37216500889834</v>
+        <v>19.64458768715197</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08618874884672852</v>
+        <v>0.08588674150641416</v>
       </c>
       <c r="C30">
-        <v>994.3598988965241</v>
+        <v>983.4928796647439</v>
       </c>
       <c r="D30">
-        <v>1137.631898896524</v>
+        <v>1141.038879664744</v>
       </c>
       <c r="E30">
-        <v>-554.1279999999999</v>
+        <v>-539.8539999999998</v>
       </c>
       <c r="F30">
-        <v>399.6720000000001</v>
+        <v>413.9460000000001</v>
       </c>
       <c r="G30">
         <v>256.4</v>
@@ -3747,28 +3747,28 @@
         <v>394.925</v>
       </c>
       <c r="M30">
-        <v>20.1035016</v>
+        <v>20.8214838</v>
       </c>
       <c r="N30">
-        <v>374.8214983999999</v>
+        <v>374.1035161999999</v>
       </c>
       <c r="O30">
-        <v>131.18752444</v>
+        <v>130.93623067</v>
       </c>
       <c r="P30">
-        <v>243.63397396</v>
+        <v>243.16728553</v>
       </c>
       <c r="Q30">
-        <v>285.83397396</v>
+        <v>285.3672855299999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1069918733982341</v>
+        <v>0.1076129457836819</v>
       </c>
       <c r="T30">
-        <v>0.8904163179743697</v>
+        <v>0.8994536779363219</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>19.64458768715197</v>
+        <v>18.96718811173293</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08588674150641416</v>
+        <v>0.0855847341660998</v>
       </c>
       <c r="C31">
-        <v>983.4928796647441</v>
+        <v>972.6463281863519</v>
       </c>
       <c r="D31">
-        <v>1141.038879664744</v>
+        <v>1144.466328186352</v>
       </c>
       <c r="E31">
-        <v>-539.854</v>
+        <v>-525.5799999999999</v>
       </c>
       <c r="F31">
-        <v>413.946</v>
+        <v>428.22</v>
       </c>
       <c r="G31">
         <v>256.4</v>
@@ -3829,28 +3829,28 @@
         <v>394.925</v>
       </c>
       <c r="M31">
-        <v>20.8214838</v>
+        <v>21.539466</v>
       </c>
       <c r="N31">
-        <v>374.1035161999999</v>
+        <v>373.385534</v>
       </c>
       <c r="O31">
-        <v>130.93623067</v>
+        <v>130.6849369</v>
       </c>
       <c r="P31">
-        <v>243.16728553</v>
+        <v>242.7005971</v>
       </c>
       <c r="Q31">
-        <v>285.3672855299999</v>
+        <v>284.9005971</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1076129457836819</v>
+        <v>0.1082517630944283</v>
       </c>
       <c r="T31">
-        <v>0.8994536779363219</v>
+        <v>0.9087492481829011</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>18.96718811173294</v>
+        <v>18.33494850800851</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0855847341660998</v>
+        <v>0.08528272682578546</v>
       </c>
       <c r="C32">
-        <v>972.6463281863519</v>
+        <v>961.8204294599387</v>
       </c>
       <c r="D32">
-        <v>1144.466328186352</v>
+        <v>1147.914429459939</v>
       </c>
       <c r="E32">
-        <v>-525.5799999999999</v>
+        <v>-511.3059999999999</v>
       </c>
       <c r="F32">
-        <v>428.22</v>
+        <v>442.494</v>
       </c>
       <c r="G32">
         <v>256.4</v>
@@ -3911,28 +3911,28 @@
         <v>394.925</v>
       </c>
       <c r="M32">
-        <v>21.539466</v>
+        <v>22.2574482</v>
       </c>
       <c r="N32">
-        <v>373.385534</v>
+        <v>372.6675518</v>
       </c>
       <c r="O32">
-        <v>130.6849369</v>
+        <v>130.43364313</v>
       </c>
       <c r="P32">
-        <v>242.7005971</v>
+        <v>242.23390867</v>
       </c>
       <c r="Q32">
-        <v>284.9005971</v>
+        <v>284.4339086699999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1082517630944283</v>
+        <v>0.1089090968489644</v>
       </c>
       <c r="T32">
-        <v>0.9087492481829011</v>
+        <v>0.9183142552482221</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>18.33494850800851</v>
+        <v>17.74349855613726</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08528272682578546</v>
+        <v>0.08498071948547109</v>
       </c>
       <c r="C33">
-        <v>961.8204294599387</v>
+        <v>951.0153707203244</v>
       </c>
       <c r="D33">
-        <v>1147.914429459939</v>
+        <v>1151.383370720325</v>
       </c>
       <c r="E33">
-        <v>-511.3059999999999</v>
+        <v>-497.0319999999999</v>
       </c>
       <c r="F33">
-        <v>442.494</v>
+        <v>456.768</v>
       </c>
       <c r="G33">
         <v>256.4</v>
@@ -3993,28 +3993,28 @@
         <v>394.925</v>
       </c>
       <c r="M33">
-        <v>22.2574482</v>
+        <v>22.9754304</v>
       </c>
       <c r="N33">
-        <v>372.6675518</v>
+        <v>371.9495696</v>
       </c>
       <c r="O33">
-        <v>130.43364313</v>
+        <v>130.18234936</v>
       </c>
       <c r="P33">
-        <v>242.23390867</v>
+        <v>241.76722024</v>
       </c>
       <c r="Q33">
-        <v>284.4339086699999</v>
+        <v>283.96722024</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1089090968489644</v>
+        <v>0.1095857639492222</v>
       </c>
       <c r="T33">
-        <v>0.9183142552482221</v>
+        <v>0.9281605860507581</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>17.74349855613726</v>
+        <v>17.18901422625797</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08498071948547109</v>
+        <v>0.08467871214515675</v>
       </c>
       <c r="C34">
-        <v>951.0153707203244</v>
+        <v>940.2313414724457</v>
       </c>
       <c r="D34">
-        <v>1151.383370720325</v>
+        <v>1154.873341472446</v>
       </c>
       <c r="E34">
-        <v>-497.0319999999999</v>
+        <v>-482.7579999999999</v>
       </c>
       <c r="F34">
-        <v>456.768</v>
+        <v>471.042</v>
       </c>
       <c r="G34">
         <v>256.4</v>
@@ -4075,28 +4075,28 @@
         <v>394.925</v>
       </c>
       <c r="M34">
-        <v>22.9754304</v>
+        <v>23.6934126</v>
       </c>
       <c r="N34">
-        <v>371.9495696</v>
+        <v>371.2315874</v>
       </c>
       <c r="O34">
-        <v>130.18234936</v>
+        <v>129.93105559</v>
       </c>
       <c r="P34">
-        <v>241.76722024</v>
+        <v>241.30053181</v>
       </c>
       <c r="Q34">
-        <v>283.96722024</v>
+        <v>283.50053181</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1095857639492222</v>
+        <v>0.1102826300673981</v>
       </c>
       <c r="T34">
-        <v>0.9281605860507581</v>
+        <v>0.9383008371757581</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>17.18901422625797</v>
+        <v>16.66813500728046</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08467871214515675</v>
+        <v>0.08437670480484238</v>
       </c>
       <c r="C35">
-        <v>940.2313414724457</v>
+        <v>929.4685335258675</v>
       </c>
       <c r="D35">
-        <v>1154.873341472446</v>
+        <v>1158.384533525867</v>
       </c>
       <c r="E35">
-        <v>-482.7579999999999</v>
+        <v>-468.4839999999999</v>
       </c>
       <c r="F35">
-        <v>471.042</v>
+        <v>485.3160000000001</v>
       </c>
       <c r="G35">
         <v>256.4</v>
@@ -4157,28 +4157,28 @@
         <v>394.925</v>
       </c>
       <c r="M35">
-        <v>23.6934126</v>
+        <v>24.4113948</v>
       </c>
       <c r="N35">
-        <v>371.2315874</v>
+        <v>370.5136052</v>
       </c>
       <c r="O35">
-        <v>129.93105559</v>
+        <v>129.67976182</v>
       </c>
       <c r="P35">
-        <v>241.30053181</v>
+        <v>240.83384338</v>
       </c>
       <c r="Q35">
-        <v>283.50053181</v>
+        <v>283.03384338</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1102826300673981</v>
+        <v>0.1110006133406703</v>
       </c>
       <c r="T35">
-        <v>0.9383008371757581</v>
+        <v>0.9487483686378793</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>16.66813500728046</v>
+        <v>16.17789574236044</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08437670480484238</v>
+        <v>0.08407469746452802</v>
       </c>
       <c r="C36">
-        <v>929.4685335258675</v>
+        <v>918.7271410299227</v>
       </c>
       <c r="D36">
-        <v>1158.384533525867</v>
+        <v>1161.917141029923</v>
       </c>
       <c r="E36">
-        <v>-468.4839999999999</v>
+        <v>-454.2099999999999</v>
       </c>
       <c r="F36">
-        <v>485.3160000000001</v>
+        <v>499.5900000000001</v>
       </c>
       <c r="G36">
         <v>256.4</v>
@@ -4239,28 +4239,28 @@
         <v>394.925</v>
       </c>
       <c r="M36">
-        <v>24.4113948</v>
+        <v>25.129377</v>
       </c>
       <c r="N36">
-        <v>370.5136052</v>
+        <v>369.795623</v>
       </c>
       <c r="O36">
-        <v>129.67976182</v>
+        <v>129.42846805</v>
       </c>
       <c r="P36">
-        <v>240.83384338</v>
+        <v>240.36715495</v>
       </c>
       <c r="Q36">
-        <v>283.03384338</v>
+        <v>282.56715495</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1110006133406703</v>
+        <v>0.1117406884069662</v>
       </c>
       <c r="T36">
-        <v>0.9487483686378793</v>
+        <v>0.9595173626065271</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>16.17789574236044</v>
+        <v>15.71567014972158</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08407469746452802</v>
+        <v>0.08377269012421368</v>
       </c>
       <c r="C37">
-        <v>918.7271410299227</v>
+        <v>908.0073605094984</v>
       </c>
       <c r="D37">
-        <v>1161.917141029923</v>
+        <v>1165.471360509498</v>
       </c>
       <c r="E37">
-        <v>-454.2099999999999</v>
+        <v>-439.9359999999998</v>
       </c>
       <c r="F37">
-        <v>499.5900000000001</v>
+        <v>513.8640000000001</v>
       </c>
       <c r="G37">
         <v>256.4</v>
@@ -4321,28 +4321,28 @@
         <v>394.925</v>
       </c>
       <c r="M37">
-        <v>25.129377</v>
+        <v>25.84735920000001</v>
       </c>
       <c r="N37">
-        <v>369.795623</v>
+        <v>369.0776407999999</v>
       </c>
       <c r="O37">
-        <v>129.42846805</v>
+        <v>129.17717428</v>
       </c>
       <c r="P37">
-        <v>240.36715495</v>
+        <v>239.90046652</v>
       </c>
       <c r="Q37">
-        <v>282.56715495</v>
+        <v>282.1004665199999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1117406884069662</v>
+        <v>0.1125038908190839</v>
       </c>
       <c r="T37">
-        <v>0.9595173626065271</v>
+        <v>0.9706228876366952</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>15.71567014972158</v>
+        <v>15.27912375667375</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08377269012421368</v>
+        <v>0.08347068278389932</v>
       </c>
       <c r="C38">
-        <v>908.0073605094985</v>
+        <v>897.3093909014818</v>
       </c>
       <c r="D38">
-        <v>1165.471360509498</v>
+        <v>1169.047390901482</v>
       </c>
       <c r="E38">
-        <v>-439.9359999999999</v>
+        <v>-425.6619999999999</v>
       </c>
       <c r="F38">
-        <v>513.864</v>
+        <v>528.138</v>
       </c>
       <c r="G38">
         <v>256.4</v>
@@ -4403,28 +4403,28 @@
         <v>394.925</v>
       </c>
       <c r="M38">
-        <v>25.8473592</v>
+        <v>26.5653414</v>
       </c>
       <c r="N38">
-        <v>369.0776407999999</v>
+        <v>368.3596585999999</v>
       </c>
       <c r="O38">
-        <v>129.17717428</v>
+        <v>128.92588051</v>
       </c>
       <c r="P38">
-        <v>239.90046652</v>
+        <v>239.43377809</v>
       </c>
       <c r="Q38">
-        <v>282.1004665199999</v>
+        <v>281.63377809</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1125038908190839</v>
+        <v>0.1132913218792053</v>
       </c>
       <c r="T38">
-        <v>0.9706228876366952</v>
+        <v>0.9820809690170273</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>15.27912375667375</v>
+        <v>14.86617446595284</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08347068278389932</v>
+        <v>0.08316867544358494</v>
       </c>
       <c r="C39">
-        <v>897.3093909014818</v>
+        <v>886.6334335918766</v>
       </c>
       <c r="D39">
-        <v>1169.047390901482</v>
+        <v>1172.645433591877</v>
       </c>
       <c r="E39">
-        <v>-425.6619999999999</v>
+        <v>-411.3879999999999</v>
       </c>
       <c r="F39">
-        <v>528.138</v>
+        <v>542.412</v>
       </c>
       <c r="G39">
         <v>256.4</v>
@@ -4485,28 +4485,28 @@
         <v>394.925</v>
       </c>
       <c r="M39">
-        <v>26.5653414</v>
+        <v>27.2833236</v>
       </c>
       <c r="N39">
-        <v>368.3596585999999</v>
+        <v>367.6416763999999</v>
       </c>
       <c r="O39">
-        <v>128.92588051</v>
+        <v>128.67458674</v>
       </c>
       <c r="P39">
-        <v>239.43377809</v>
+        <v>238.96708966</v>
       </c>
       <c r="Q39">
-        <v>281.63377809</v>
+        <v>281.16708966</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1132913218792053</v>
+        <v>0.1141041539412661</v>
       </c>
       <c r="T39">
-        <v>0.9820809690170273</v>
+        <v>0.9939086659257574</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>14.86617446595284</v>
+        <v>14.47495934842777</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08316867544358494</v>
+        <v>0.08286666810327062</v>
       </c>
       <c r="C40">
-        <v>886.6334335918766</v>
+        <v>875.9796924536068</v>
       </c>
       <c r="D40">
-        <v>1172.645433591877</v>
+        <v>1176.265692453607</v>
       </c>
       <c r="E40">
-        <v>-411.3879999999999</v>
+        <v>-397.1139999999999</v>
       </c>
       <c r="F40">
-        <v>542.412</v>
+        <v>556.686</v>
       </c>
       <c r="G40">
         <v>256.4</v>
@@ -4567,28 +4567,28 @@
         <v>394.925</v>
       </c>
       <c r="M40">
-        <v>27.2833236</v>
+        <v>28.0013058</v>
       </c>
       <c r="N40">
-        <v>367.6416763999999</v>
+        <v>366.9236941999999</v>
       </c>
       <c r="O40">
-        <v>128.67458674</v>
+        <v>128.42329297</v>
       </c>
       <c r="P40">
-        <v>238.96708966</v>
+        <v>238.50040123</v>
       </c>
       <c r="Q40">
-        <v>281.16708966</v>
+        <v>280.70040123</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1141041539412661</v>
+        <v>0.1149436362348699</v>
       </c>
       <c r="T40">
-        <v>0.9939086659257574</v>
+        <v>1.006124156175757</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>14.47495934842777</v>
+        <v>14.10380654462193</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08286666810327062</v>
+        <v>0.08256466076295625</v>
       </c>
       <c r="C41">
-        <v>875.9796924536068</v>
+        <v>865.3483738850296</v>
       </c>
       <c r="D41">
-        <v>1176.265692453607</v>
+        <v>1179.90837388503</v>
       </c>
       <c r="E41">
-        <v>-397.1139999999999</v>
+        <v>-382.8399999999999</v>
       </c>
       <c r="F41">
-        <v>556.686</v>
+        <v>570.96</v>
       </c>
       <c r="G41">
         <v>256.4</v>
@@ -4649,28 +4649,28 @@
         <v>394.925</v>
       </c>
       <c r="M41">
-        <v>28.0013058</v>
+        <v>28.719288</v>
       </c>
       <c r="N41">
-        <v>366.9236941999999</v>
+        <v>366.2057119999999</v>
       </c>
       <c r="O41">
-        <v>128.42329297</v>
+        <v>128.1719992</v>
       </c>
       <c r="P41">
-        <v>238.50040123</v>
+        <v>238.0337128</v>
       </c>
       <c r="Q41">
-        <v>280.70040123</v>
+        <v>280.2337127999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1149436362348699</v>
+        <v>0.1158111012715937</v>
       </c>
       <c r="T41">
-        <v>1.006124156175757</v>
+        <v>1.01874682943409</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>14.10380654462193</v>
+        <v>13.75121138100638</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08256466076295625</v>
+        <v>0.08226265342264187</v>
       </c>
       <c r="C42">
-        <v>865.3483738850296</v>
+        <v>854.739686849155</v>
       </c>
       <c r="D42">
-        <v>1179.90837388503</v>
+        <v>1183.573686849155</v>
       </c>
       <c r="E42">
-        <v>-382.8399999999999</v>
+        <v>-368.5659999999999</v>
       </c>
       <c r="F42">
-        <v>570.96</v>
+        <v>585.234</v>
       </c>
       <c r="G42">
         <v>256.4</v>
@@ -4731,28 +4731,28 @@
         <v>394.925</v>
       </c>
       <c r="M42">
-        <v>28.719288</v>
+        <v>29.4372702</v>
       </c>
       <c r="N42">
-        <v>366.2057119999999</v>
+        <v>365.4877298</v>
       </c>
       <c r="O42">
-        <v>128.1719992</v>
+        <v>127.92070543</v>
       </c>
       <c r="P42">
-        <v>238.0337128</v>
+        <v>237.56702437</v>
       </c>
       <c r="Q42">
-        <v>280.2337127999999</v>
+        <v>279.7670243699999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1158111012715937</v>
+        <v>0.1167079719027828</v>
       </c>
       <c r="T42">
-        <v>1.01874682943409</v>
+        <v>1.03179738992152</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>13.75121138100638</v>
+        <v>13.41581598146964</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08226265342264187</v>
+        <v>0.08196064608232753</v>
       </c>
       <c r="C43">
-        <v>854.739686849155</v>
+        <v>844.1538429136068</v>
       </c>
       <c r="D43">
-        <v>1183.573686849155</v>
+        <v>1187.261842913607</v>
       </c>
       <c r="E43">
-        <v>-368.5659999999999</v>
+        <v>-354.2919999999998</v>
       </c>
       <c r="F43">
-        <v>585.234</v>
+        <v>599.5080000000002</v>
       </c>
       <c r="G43">
         <v>256.4</v>
@@ -4813,28 +4813,28 @@
         <v>394.925</v>
       </c>
       <c r="M43">
-        <v>29.4372702</v>
+        <v>30.15525240000001</v>
       </c>
       <c r="N43">
-        <v>365.4877298</v>
+        <v>364.7697476</v>
       </c>
       <c r="O43">
-        <v>127.92070543</v>
+        <v>127.66941166</v>
       </c>
       <c r="P43">
-        <v>237.56702437</v>
+        <v>237.10033594</v>
       </c>
       <c r="Q43">
-        <v>279.7670243699999</v>
+        <v>279.30033594</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1167079719027828</v>
+        <v>0.1176357691074613</v>
       </c>
       <c r="T43">
-        <v>1.03179738992152</v>
+        <v>1.045297969736102</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>13.41581598146964</v>
+        <v>13.09639179143465</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08196064608232755</v>
+        <v>0.08207788874201317</v>
       </c>
       <c r="C44">
-        <v>844.1538429136069</v>
+        <v>828.4453328202436</v>
       </c>
       <c r="D44">
-        <v>1187.261842913607</v>
+        <v>1185.827332820244</v>
       </c>
       <c r="E44">
-        <v>-354.2919999999999</v>
+        <v>-340.0179999999999</v>
       </c>
       <c r="F44">
-        <v>599.508</v>
+        <v>613.782</v>
       </c>
       <c r="G44">
         <v>256.4</v>
@@ -4895,45 +4895,45 @@
         <v>394.925</v>
       </c>
       <c r="M44">
-        <v>30.1552524</v>
+        <v>31.7939076</v>
       </c>
       <c r="N44">
-        <v>364.7697476</v>
+        <v>363.1310923999999</v>
       </c>
       <c r="O44">
-        <v>127.66941166</v>
+        <v>127.09588234</v>
       </c>
       <c r="P44">
-        <v>237.10033594</v>
+        <v>236.03521006</v>
       </c>
       <c r="Q44">
-        <v>279.30033594</v>
+        <v>278.23521006</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1176357691074613</v>
+        <v>0.1185961206000231</v>
       </c>
       <c r="T44">
-        <v>1.045297969736102</v>
+        <v>1.059272254105581</v>
       </c>
       <c r="U44">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V44">
         <v>0.35</v>
       </c>
       <c r="W44">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y44">
-        <v>13.09639179143465</v>
+        <v>12.42140491092073</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08207788874201317</v>
+        <v>0.08178563140169882</v>
       </c>
       <c r="C45">
-        <v>828.4453328202436</v>
+        <v>817.7536854570053</v>
       </c>
       <c r="D45">
-        <v>1185.827332820244</v>
+        <v>1189.409685457005</v>
       </c>
       <c r="E45">
-        <v>-340.0179999999999</v>
+        <v>-325.7439999999999</v>
       </c>
       <c r="F45">
-        <v>613.782</v>
+        <v>628.056</v>
       </c>
       <c r="G45">
         <v>256.4</v>
@@ -4977,28 +4977,28 @@
         <v>394.925</v>
       </c>
       <c r="M45">
-        <v>31.7939076</v>
+        <v>32.5333008</v>
       </c>
       <c r="N45">
-        <v>363.1310923999999</v>
+        <v>362.3916991999999</v>
       </c>
       <c r="O45">
-        <v>127.09588234</v>
+        <v>126.83709472</v>
       </c>
       <c r="P45">
-        <v>236.03521006</v>
+        <v>235.55460448</v>
       </c>
       <c r="Q45">
-        <v>278.23521006</v>
+        <v>277.75460448</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1185961206000231</v>
+        <v>0.1195907703601765</v>
       </c>
       <c r="T45">
-        <v>1.059272254105581</v>
+        <v>1.073745620059685</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>12.42140491092073</v>
+        <v>12.13910025385435</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08178563140169882</v>
+        <v>0.08149337406138446</v>
       </c>
       <c r="C46">
-        <v>817.7536854570053</v>
+        <v>807.083748061886</v>
       </c>
       <c r="D46">
-        <v>1189.409685457005</v>
+        <v>1193.013748061886</v>
       </c>
       <c r="E46">
-        <v>-325.7439999999999</v>
+        <v>-311.4699999999999</v>
       </c>
       <c r="F46">
-        <v>628.056</v>
+        <v>642.33</v>
       </c>
       <c r="G46">
         <v>256.4</v>
@@ -5059,28 +5059,28 @@
         <v>394.925</v>
       </c>
       <c r="M46">
-        <v>32.5333008</v>
+        <v>33.272694</v>
       </c>
       <c r="N46">
-        <v>362.3916991999999</v>
+        <v>361.652306</v>
       </c>
       <c r="O46">
-        <v>126.83709472</v>
+        <v>126.5783071</v>
       </c>
       <c r="P46">
-        <v>235.55460448</v>
+        <v>235.0739989</v>
       </c>
       <c r="Q46">
-        <v>277.75460448</v>
+        <v>277.2739989</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1195907703601765</v>
+        <v>0.1206215892025172</v>
       </c>
       <c r="T46">
-        <v>1.073745620059685</v>
+        <v>1.088745290230302</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>12.13910025385435</v>
+        <v>11.86934247043536</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08149337406138446</v>
+        <v>0.08120111672107011</v>
       </c>
       <c r="C47">
-        <v>807.083748061886</v>
+        <v>796.4357185865967</v>
       </c>
       <c r="D47">
-        <v>1193.013748061886</v>
+        <v>1196.639718586597</v>
       </c>
       <c r="E47">
-        <v>-311.4699999999999</v>
+        <v>-297.1959999999999</v>
       </c>
       <c r="F47">
-        <v>642.33</v>
+        <v>656.604</v>
       </c>
       <c r="G47">
         <v>256.4</v>
@@ -5141,28 +5141,28 @@
         <v>394.925</v>
       </c>
       <c r="M47">
-        <v>33.272694</v>
+        <v>34.0120872</v>
       </c>
       <c r="N47">
-        <v>361.652306</v>
+        <v>360.9129128</v>
       </c>
       <c r="O47">
-        <v>126.5783071</v>
+        <v>126.31951948</v>
       </c>
       <c r="P47">
-        <v>235.0739989</v>
+        <v>234.59339332</v>
       </c>
       <c r="Q47">
-        <v>277.2739989</v>
+        <v>276.79339332</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1206215892025172</v>
+        <v>0.1216905865205002</v>
       </c>
       <c r="T47">
-        <v>1.088745290230302</v>
+        <v>1.104300503740571</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>11.86934247043536</v>
+        <v>11.61131328629546</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08120111672107011</v>
+        <v>0.08090885938075576</v>
       </c>
       <c r="C48">
-        <v>796.4357185865967</v>
+        <v>785.8097973967534</v>
       </c>
       <c r="D48">
-        <v>1196.639718586597</v>
+        <v>1200.287797396753</v>
       </c>
       <c r="E48">
-        <v>-297.1959999999999</v>
+        <v>-282.9219999999999</v>
       </c>
       <c r="F48">
-        <v>656.604</v>
+        <v>670.878</v>
       </c>
       <c r="G48">
         <v>256.4</v>
@@ -5223,28 +5223,28 @@
         <v>394.925</v>
       </c>
       <c r="M48">
-        <v>34.0120872</v>
+        <v>34.7514804</v>
       </c>
       <c r="N48">
-        <v>360.9129128</v>
+        <v>360.1735196</v>
       </c>
       <c r="O48">
-        <v>126.31951948</v>
+        <v>126.06073186</v>
       </c>
       <c r="P48">
-        <v>234.59339332</v>
+        <v>234.11278774</v>
       </c>
       <c r="Q48">
-        <v>276.79339332</v>
+        <v>276.31278774</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1216905865205002</v>
+        <v>0.1227999233599165</v>
       </c>
       <c r="T48">
-        <v>1.104300503740571</v>
+        <v>1.120442706439907</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>11.61131328629546</v>
+        <v>11.36426406743812</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08090885938075576</v>
+        <v>0.08061660204044138</v>
       </c>
       <c r="C49">
-        <v>785.8097973967534</v>
+        <v>775.206187308785</v>
       </c>
       <c r="D49">
-        <v>1200.287797396753</v>
+        <v>1203.958187308785</v>
       </c>
       <c r="E49">
-        <v>-282.9219999999999</v>
+        <v>-268.6479999999999</v>
       </c>
       <c r="F49">
-        <v>670.878</v>
+        <v>685.152</v>
       </c>
       <c r="G49">
         <v>256.4</v>
@@ -5305,28 +5305,28 @@
         <v>394.925</v>
       </c>
       <c r="M49">
-        <v>34.7514804</v>
+        <v>35.4908736</v>
       </c>
       <c r="N49">
-        <v>360.1735196</v>
+        <v>359.4341264</v>
       </c>
       <c r="O49">
-        <v>126.06073186</v>
+        <v>125.80194424</v>
       </c>
       <c r="P49">
-        <v>234.11278774</v>
+        <v>233.63218216</v>
       </c>
       <c r="Q49">
-        <v>276.31278774</v>
+        <v>275.83218216</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1227999233599165</v>
+        <v>0.1239519270008488</v>
       </c>
       <c r="T49">
-        <v>1.120442706439907</v>
+        <v>1.137205763089217</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>11.36426406743812</v>
+        <v>11.12750856603316</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08061660204044138</v>
+        <v>0.08032434470012703</v>
       </c>
       <c r="C50">
-        <v>775.206187308785</v>
+        <v>764.6250936275177</v>
       </c>
       <c r="D50">
-        <v>1203.958187308785</v>
+        <v>1207.651093627518</v>
       </c>
       <c r="E50">
-        <v>-268.6479999999999</v>
+        <v>-254.3739999999999</v>
       </c>
       <c r="F50">
-        <v>685.152</v>
+        <v>699.426</v>
       </c>
       <c r="G50">
         <v>256.4</v>
@@ -5387,28 +5387,28 @@
         <v>394.925</v>
       </c>
       <c r="M50">
-        <v>35.4908736</v>
+        <v>36.2302668</v>
       </c>
       <c r="N50">
-        <v>359.4341264</v>
+        <v>358.6947332</v>
       </c>
       <c r="O50">
-        <v>125.80194424</v>
+        <v>125.54315662</v>
       </c>
       <c r="P50">
-        <v>233.63218216</v>
+        <v>233.15157658</v>
       </c>
       <c r="Q50">
-        <v>275.83218216</v>
+        <v>275.35157658</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1239519270008488</v>
+        <v>0.125149107255151</v>
       </c>
       <c r="T50">
-        <v>1.137205763089217</v>
+        <v>1.154626194509089</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>11.12750856603316</v>
+        <v>10.90041655448146</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08032434470012703</v>
+        <v>0.08003208735981268</v>
       </c>
       <c r="C51">
-        <v>764.6250936275177</v>
+        <v>754.0667241844578</v>
       </c>
       <c r="D51">
-        <v>1207.651093627518</v>
+        <v>1211.366724184458</v>
       </c>
       <c r="E51">
-        <v>-254.3739999999999</v>
+        <v>-240.0999999999999</v>
       </c>
       <c r="F51">
-        <v>699.426</v>
+        <v>713.7</v>
       </c>
       <c r="G51">
         <v>256.4</v>
@@ -5469,28 +5469,28 @@
         <v>394.925</v>
       </c>
       <c r="M51">
-        <v>36.2302668</v>
+        <v>36.96966</v>
       </c>
       <c r="N51">
-        <v>358.6947332</v>
+        <v>357.95534</v>
       </c>
       <c r="O51">
-        <v>125.54315662</v>
+        <v>125.284369</v>
       </c>
       <c r="P51">
-        <v>233.15157658</v>
+        <v>232.670971</v>
       </c>
       <c r="Q51">
-        <v>275.35157658</v>
+        <v>274.870971</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.125149107255151</v>
+        <v>0.1263941747196254</v>
       </c>
       <c r="T51">
-        <v>1.154626194509089</v>
+        <v>1.172743443185755</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>10.90041655448146</v>
+        <v>10.68240822339183</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08003208735981268</v>
+        <v>0.07973983001949832</v>
       </c>
       <c r="C52">
-        <v>754.0667241844578</v>
+        <v>743.5312893767824</v>
       </c>
       <c r="D52">
-        <v>1211.366724184458</v>
+        <v>1215.105289376783</v>
       </c>
       <c r="E52">
-        <v>-240.0999999999999</v>
+        <v>-225.8259999999999</v>
       </c>
       <c r="F52">
-        <v>713.7</v>
+        <v>727.974</v>
       </c>
       <c r="G52">
         <v>256.4</v>
@@ -5551,28 +5551,28 @@
         <v>394.925</v>
       </c>
       <c r="M52">
-        <v>36.96966</v>
+        <v>37.7090532</v>
       </c>
       <c r="N52">
-        <v>357.95534</v>
+        <v>357.2159468</v>
       </c>
       <c r="O52">
-        <v>125.284369</v>
+        <v>125.02558138</v>
       </c>
       <c r="P52">
-        <v>232.670971</v>
+        <v>232.19036542</v>
       </c>
       <c r="Q52">
-        <v>274.870971</v>
+        <v>274.39036542</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1263941747196254</v>
+        <v>0.1276900612642823</v>
       </c>
       <c r="T52">
-        <v>1.172743443185755</v>
+        <v>1.191600171400245</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>10.68240822339183</v>
+        <v>10.47294923861944</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07973983001949832</v>
+        <v>0.07944757267918395</v>
       </c>
       <c r="C53">
-        <v>743.5312893767824</v>
+        <v>733.0190022070501</v>
       </c>
       <c r="D53">
-        <v>1215.105289376783</v>
+        <v>1218.86700220705</v>
       </c>
       <c r="E53">
-        <v>-225.8259999999999</v>
+        <v>-211.5519999999999</v>
       </c>
       <c r="F53">
-        <v>727.974</v>
+        <v>742.248</v>
       </c>
       <c r="G53">
         <v>256.4</v>
@@ -5633,28 +5633,28 @@
         <v>394.925</v>
       </c>
       <c r="M53">
-        <v>37.7090532</v>
+        <v>38.4484464</v>
       </c>
       <c r="N53">
-        <v>357.2159468</v>
+        <v>356.4765535999999</v>
       </c>
       <c r="O53">
-        <v>125.02558138</v>
+        <v>124.76679376</v>
       </c>
       <c r="P53">
-        <v>232.19036542</v>
+        <v>231.7097598399999</v>
       </c>
       <c r="Q53">
-        <v>274.39036542</v>
+        <v>273.9097598399999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1276900612642823</v>
+        <v>0.1290399430816332</v>
       </c>
       <c r="T53">
-        <v>1.191600171400245</v>
+        <v>1.211242596623672</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>10.47294923861944</v>
+        <v>10.27154636864599</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07944757267918395</v>
+        <v>0.0791553153388696</v>
       </c>
       <c r="C54">
-        <v>733.0190022070501</v>
+        <v>722.5300783236579</v>
       </c>
       <c r="D54">
-        <v>1218.86700220705</v>
+        <v>1222.652078323658</v>
       </c>
       <c r="E54">
-        <v>-211.5519999999999</v>
+        <v>-197.2779999999999</v>
       </c>
       <c r="F54">
-        <v>742.248</v>
+        <v>756.522</v>
       </c>
       <c r="G54">
         <v>256.4</v>
@@ -5715,28 +5715,28 @@
         <v>394.925</v>
       </c>
       <c r="M54">
-        <v>38.4484464</v>
+        <v>39.1878396</v>
       </c>
       <c r="N54">
-        <v>356.4765535999999</v>
+        <v>355.7371603999999</v>
       </c>
       <c r="O54">
-        <v>124.76679376</v>
+        <v>124.50800614</v>
       </c>
       <c r="P54">
-        <v>231.7097598399999</v>
+        <v>231.22915426</v>
       </c>
       <c r="Q54">
-        <v>273.9097598399999</v>
+        <v>273.42915426</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1290399430816332</v>
+        <v>0.130447266678446</v>
       </c>
       <c r="T54">
-        <v>1.211242596623672</v>
+        <v>1.231720869728946</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>10.27154636864599</v>
+        <v>10.07774360697342</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0791553153388696</v>
+        <v>0.07886305799855524</v>
       </c>
       <c r="C55">
-        <v>722.5300783236579</v>
+        <v>712.064736062049</v>
       </c>
       <c r="D55">
-        <v>1222.652078323658</v>
+        <v>1226.460736062049</v>
       </c>
       <c r="E55">
-        <v>-197.2779999999999</v>
+        <v>-183.0039999999999</v>
       </c>
       <c r="F55">
-        <v>756.522</v>
+        <v>770.796</v>
       </c>
       <c r="G55">
         <v>256.4</v>
@@ -5797,28 +5797,28 @@
         <v>394.925</v>
       </c>
       <c r="M55">
-        <v>39.1878396</v>
+        <v>39.9272328</v>
       </c>
       <c r="N55">
-        <v>355.7371603999999</v>
+        <v>354.9977671999999</v>
       </c>
       <c r="O55">
-        <v>124.50800614</v>
+        <v>124.24921852</v>
       </c>
       <c r="P55">
-        <v>231.22915426</v>
+        <v>230.74854868</v>
       </c>
       <c r="Q55">
-        <v>273.42915426</v>
+        <v>272.9485486799999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.130447266678446</v>
+        <v>0.1319157782577288</v>
       </c>
       <c r="T55">
-        <v>1.231720869728946</v>
+        <v>1.25308950253445</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>10.07774360697342</v>
+        <v>9.891118725362805</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07886305799855524</v>
+        <v>0.07917855065824089</v>
       </c>
       <c r="C56">
-        <v>712.064736062049</v>
+        <v>693.6802936379104</v>
       </c>
       <c r="D56">
-        <v>1226.460736062049</v>
+        <v>1222.350293637911</v>
       </c>
       <c r="E56">
-        <v>-183.0039999999999</v>
+        <v>-168.7299999999998</v>
       </c>
       <c r="F56">
-        <v>770.796</v>
+        <v>785.0700000000002</v>
       </c>
       <c r="G56">
         <v>256.4</v>
@@ -5879,45 +5879,45 @@
         <v>394.925</v>
       </c>
       <c r="M56">
-        <v>39.9272328</v>
+        <v>42.001245</v>
       </c>
       <c r="N56">
-        <v>354.9977671999999</v>
+        <v>352.923755</v>
       </c>
       <c r="O56">
-        <v>124.24921852</v>
+        <v>123.52331425</v>
       </c>
       <c r="P56">
-        <v>230.74854868</v>
+        <v>229.40044075</v>
       </c>
       <c r="Q56">
-        <v>272.9485486799999</v>
+        <v>271.60044075</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1319157782577288</v>
+        <v>0.1334495570183131</v>
       </c>
       <c r="T56">
-        <v>1.25308950253445</v>
+        <v>1.275407852353532</v>
       </c>
       <c r="U56">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V56">
         <v>0.35</v>
       </c>
       <c r="W56">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>9.891118725362805</v>
+        <v>9.402697467658397</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07917855065824089</v>
+        <v>0.07889734331792653</v>
       </c>
       <c r="C57">
-        <v>693.6802936379104</v>
+        <v>683.0687063672871</v>
       </c>
       <c r="D57">
-        <v>1222.350293637911</v>
+        <v>1226.012706367287</v>
       </c>
       <c r="E57">
-        <v>-168.7299999999998</v>
+        <v>-154.4559999999998</v>
       </c>
       <c r="F57">
-        <v>785.0700000000002</v>
+        <v>799.3440000000002</v>
       </c>
       <c r="G57">
         <v>256.4</v>
@@ -5961,28 +5961,28 @@
         <v>394.925</v>
       </c>
       <c r="M57">
-        <v>42.001245</v>
+        <v>42.76490400000001</v>
       </c>
       <c r="N57">
-        <v>352.923755</v>
+        <v>352.160096</v>
       </c>
       <c r="O57">
-        <v>123.52331425</v>
+        <v>123.2560336</v>
       </c>
       <c r="P57">
-        <v>229.40044075</v>
+        <v>228.9040624</v>
       </c>
       <c r="Q57">
-        <v>271.60044075</v>
+        <v>271.1040624</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1334495570183131</v>
+        <v>0.1350530529952876</v>
       </c>
       <c r="T57">
-        <v>1.275407852353532</v>
+        <v>1.298740672618936</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>9.402697467658397</v>
+        <v>9.234792155735924</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07889734331792653</v>
+        <v>0.07861613597761218</v>
       </c>
       <c r="C58">
-        <v>683.0687063672871</v>
+        <v>672.4791317337142</v>
       </c>
       <c r="D58">
-        <v>1226.012706367287</v>
+        <v>1229.697131733714</v>
       </c>
       <c r="E58">
-        <v>-154.4559999999998</v>
+        <v>-140.1819999999998</v>
       </c>
       <c r="F58">
-        <v>799.3440000000002</v>
+        <v>813.6180000000002</v>
       </c>
       <c r="G58">
         <v>256.4</v>
@@ -6043,28 +6043,28 @@
         <v>394.925</v>
       </c>
       <c r="M58">
-        <v>42.76490400000001</v>
+        <v>43.52856300000001</v>
       </c>
       <c r="N58">
-        <v>352.160096</v>
+        <v>351.3964369999999</v>
       </c>
       <c r="O58">
-        <v>123.2560336</v>
+        <v>122.98875295</v>
       </c>
       <c r="P58">
-        <v>228.9040624</v>
+        <v>228.40768405</v>
       </c>
       <c r="Q58">
-        <v>271.1040624</v>
+        <v>270.60768405</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1350530529952876</v>
+        <v>0.1367311301804935</v>
       </c>
       <c r="T58">
-        <v>1.298740672618936</v>
+        <v>1.323158740338544</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>9.234792155735924</v>
+        <v>9.072778258266874</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07861613597761218</v>
+        <v>0.07833492863729782</v>
       </c>
       <c r="C59">
-        <v>672.4791317337142</v>
+        <v>661.9117687931727</v>
       </c>
       <c r="D59">
-        <v>1229.697131733714</v>
+        <v>1233.403768793173</v>
       </c>
       <c r="E59">
-        <v>-140.1819999999998</v>
+        <v>-125.9079999999998</v>
       </c>
       <c r="F59">
-        <v>813.6180000000002</v>
+        <v>827.8920000000002</v>
       </c>
       <c r="G59">
         <v>256.4</v>
@@ -6125,28 +6125,28 @@
         <v>394.925</v>
       </c>
       <c r="M59">
-        <v>43.52856300000001</v>
+        <v>44.29222200000001</v>
       </c>
       <c r="N59">
-        <v>351.3964369999999</v>
+        <v>350.6327779999999</v>
       </c>
       <c r="O59">
-        <v>122.98875295</v>
+        <v>122.7214723</v>
       </c>
       <c r="P59">
-        <v>228.40768405</v>
+        <v>227.9113057</v>
       </c>
       <c r="Q59">
-        <v>270.60768405</v>
+        <v>270.1113056999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1367311301804935</v>
+        <v>0.1384891158030901</v>
       </c>
       <c r="T59">
-        <v>1.323158740338544</v>
+        <v>1.348739573187658</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>9.072778258266874</v>
+        <v>8.916351046917445</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07833492863729782</v>
+        <v>0.07805372129698346</v>
       </c>
       <c r="C60">
-        <v>661.9117687931729</v>
+        <v>651.366819008933</v>
       </c>
       <c r="D60">
-        <v>1233.403768793173</v>
+        <v>1237.132819008933</v>
       </c>
       <c r="E60">
-        <v>-125.908</v>
+        <v>-111.6339999999999</v>
       </c>
       <c r="F60">
-        <v>827.8919999999999</v>
+        <v>842.1660000000001</v>
       </c>
       <c r="G60">
         <v>256.4</v>
@@ -6207,28 +6207,28 @@
         <v>394.925</v>
       </c>
       <c r="M60">
-        <v>44.292222</v>
+        <v>45.055881</v>
       </c>
       <c r="N60">
-        <v>350.632778</v>
+        <v>349.869119</v>
       </c>
       <c r="O60">
-        <v>122.7214723</v>
+        <v>122.45419165</v>
       </c>
       <c r="P60">
-        <v>227.9113057</v>
+        <v>227.41492735</v>
       </c>
       <c r="Q60">
-        <v>270.1113057</v>
+        <v>269.61492735</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1384891158030901</v>
+        <v>0.1403328568219109</v>
       </c>
       <c r="T60">
-        <v>1.348739573187658</v>
+        <v>1.375568251541606</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.916351046917448</v>
+        <v>8.765226452901896</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07805372129698346</v>
+        <v>0.07777251395666909</v>
       </c>
       <c r="C61">
-        <v>651.366819008933</v>
+        <v>640.8444862880542</v>
       </c>
       <c r="D61">
-        <v>1237.132819008933</v>
+        <v>1240.884486288054</v>
       </c>
       <c r="E61">
-        <v>-111.6339999999999</v>
+        <v>-97.3599999999999</v>
       </c>
       <c r="F61">
-        <v>842.1660000000001</v>
+        <v>856.4400000000001</v>
       </c>
       <c r="G61">
         <v>256.4</v>
@@ -6289,28 +6289,28 @@
         <v>394.925</v>
       </c>
       <c r="M61">
-        <v>45.055881</v>
+        <v>45.81954</v>
       </c>
       <c r="N61">
-        <v>349.869119</v>
+        <v>349.1054599999999</v>
       </c>
       <c r="O61">
-        <v>122.45419165</v>
+        <v>122.186911</v>
       </c>
       <c r="P61">
-        <v>227.41492735</v>
+        <v>226.918549</v>
       </c>
       <c r="Q61">
-        <v>269.61492735</v>
+        <v>269.118549</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1403328568219109</v>
+        <v>0.1422687848916727</v>
       </c>
       <c r="T61">
-        <v>1.375568251541606</v>
+        <v>1.403738363813252</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.765226452901896</v>
+        <v>8.619139345353531</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07777251395666909</v>
+        <v>0.07749130661635474</v>
       </c>
       <c r="C62">
-        <v>640.8444862880542</v>
+        <v>630.3449770185529</v>
       </c>
       <c r="D62">
-        <v>1240.884486288054</v>
+        <v>1244.658977018553</v>
       </c>
       <c r="E62">
-        <v>-97.3599999999999</v>
+        <v>-83.0859999999999</v>
       </c>
       <c r="F62">
-        <v>856.4400000000001</v>
+        <v>870.7140000000001</v>
       </c>
       <c r="G62">
         <v>256.4</v>
@@ -6371,28 +6371,28 @@
         <v>394.925</v>
       </c>
       <c r="M62">
-        <v>45.81954</v>
+        <v>46.583199</v>
       </c>
       <c r="N62">
-        <v>349.1054599999999</v>
+        <v>348.341801</v>
       </c>
       <c r="O62">
-        <v>122.186911</v>
+        <v>121.91963035</v>
       </c>
       <c r="P62">
-        <v>226.918549</v>
+        <v>226.42217065</v>
       </c>
       <c r="Q62">
-        <v>269.118549</v>
+        <v>268.62217065</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1422687848916727</v>
+        <v>0.1443039913239865</v>
       </c>
       <c r="T62">
-        <v>1.403738363813252</v>
+        <v>1.433353097227034</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.619139345353531</v>
+        <v>8.47784197903626</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07749130661635474</v>
+        <v>0.0772100992760404</v>
       </c>
       <c r="C63">
-        <v>630.3449770185529</v>
+        <v>619.8685001072497</v>
       </c>
       <c r="D63">
-        <v>1244.658977018553</v>
+        <v>1248.45650010725</v>
       </c>
       <c r="E63">
-        <v>-83.0859999999999</v>
+        <v>-68.8119999999999</v>
       </c>
       <c r="F63">
-        <v>870.7140000000001</v>
+        <v>884.9880000000001</v>
       </c>
       <c r="G63">
         <v>256.4</v>
@@ -6453,28 +6453,28 @@
         <v>394.925</v>
       </c>
       <c r="M63">
-        <v>46.583199</v>
+        <v>47.346858</v>
       </c>
       <c r="N63">
-        <v>348.341801</v>
+        <v>347.578142</v>
       </c>
       <c r="O63">
-        <v>121.91963035</v>
+        <v>121.6523497</v>
       </c>
       <c r="P63">
-        <v>226.42217065</v>
+        <v>225.9257923</v>
       </c>
       <c r="Q63">
-        <v>268.62217065</v>
+        <v>268.1257922999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1443039913239865</v>
+        <v>0.1464463138843168</v>
       </c>
       <c r="T63">
-        <v>1.433353097227034</v>
+        <v>1.464526500820489</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>8.47784197903626</v>
+        <v>8.341102592277611</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0772100992760404</v>
+        <v>0.07692889193572604</v>
       </c>
       <c r="C64">
-        <v>619.8685001072497</v>
+        <v>609.4152670183154</v>
       </c>
       <c r="D64">
-        <v>1248.45650010725</v>
+        <v>1252.277267018315</v>
       </c>
       <c r="E64">
-        <v>-68.8119999999999</v>
+        <v>-54.5379999999999</v>
       </c>
       <c r="F64">
-        <v>884.9880000000001</v>
+        <v>899.2620000000001</v>
       </c>
       <c r="G64">
         <v>256.4</v>
@@ -6535,28 +6535,28 @@
         <v>394.925</v>
       </c>
       <c r="M64">
-        <v>47.346858</v>
+        <v>48.110517</v>
       </c>
       <c r="N64">
-        <v>347.578142</v>
+        <v>346.8144829999999</v>
       </c>
       <c r="O64">
-        <v>121.6523497</v>
+        <v>121.38506905</v>
       </c>
       <c r="P64">
-        <v>225.9257923</v>
+        <v>225.42941395</v>
       </c>
       <c r="Q64">
-        <v>268.1257922999999</v>
+        <v>267.62941395</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1464463138843168</v>
+        <v>0.1487044376641244</v>
       </c>
       <c r="T64">
-        <v>1.464526500820489</v>
+        <v>1.497384953256832</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>8.341102592277611</v>
+        <v>8.208704138431933</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07692889193572604</v>
+        <v>0.07664768459541169</v>
       </c>
       <c r="C65">
-        <v>609.4152670183154</v>
+        <v>598.9854918125179</v>
       </c>
       <c r="D65">
-        <v>1252.277267018315</v>
+        <v>1256.121491812518</v>
       </c>
       <c r="E65">
-        <v>-54.5379999999999</v>
+        <v>-40.2639999999999</v>
       </c>
       <c r="F65">
-        <v>899.2620000000001</v>
+        <v>913.5360000000001</v>
       </c>
       <c r="G65">
         <v>256.4</v>
@@ -6617,28 +6617,28 @@
         <v>394.925</v>
       </c>
       <c r="M65">
-        <v>48.110517</v>
+        <v>48.87417600000001</v>
       </c>
       <c r="N65">
-        <v>346.8144829999999</v>
+        <v>346.0508239999999</v>
       </c>
       <c r="O65">
-        <v>121.38506905</v>
+        <v>121.1177884</v>
       </c>
       <c r="P65">
-        <v>225.42941395</v>
+        <v>224.9330356</v>
       </c>
       <c r="Q65">
-        <v>267.62941395</v>
+        <v>267.1330356</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1487044376641244</v>
+        <v>0.1510880127650324</v>
       </c>
       <c r="T65">
-        <v>1.497384953256832</v>
+        <v>1.532068875272973</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>8.208704138431933</v>
+        <v>8.080443136268935</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07664768459541169</v>
+        <v>0.07636647725509732</v>
       </c>
       <c r="C66">
-        <v>598.9854918125179</v>
+        <v>588.5793911872041</v>
       </c>
       <c r="D66">
-        <v>1256.121491812518</v>
+        <v>1259.989391187204</v>
       </c>
       <c r="E66">
-        <v>-40.2639999999999</v>
+        <v>-25.9899999999999</v>
       </c>
       <c r="F66">
-        <v>913.5360000000001</v>
+        <v>927.8100000000001</v>
       </c>
       <c r="G66">
         <v>256.4</v>
@@ -6699,28 +6699,28 @@
         <v>394.925</v>
       </c>
       <c r="M66">
-        <v>48.87417600000001</v>
+        <v>49.637835</v>
       </c>
       <c r="N66">
-        <v>346.0508239999999</v>
+        <v>345.287165</v>
       </c>
       <c r="O66">
-        <v>121.1177884</v>
+        <v>120.85050775</v>
       </c>
       <c r="P66">
-        <v>224.9330356</v>
+        <v>224.43665725</v>
       </c>
       <c r="Q66">
-        <v>267.1330356</v>
+        <v>266.63665725</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1510880127650324</v>
+        <v>0.1536077921574209</v>
       </c>
       <c r="T66">
-        <v>1.532068875272973</v>
+        <v>1.568734735690036</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>8.080443136268935</v>
+        <v>7.956128626480183</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07636647725509732</v>
+        <v>0.07608526991478295</v>
       </c>
       <c r="C67">
-        <v>588.5793911872041</v>
+        <v>578.1971845170176</v>
       </c>
       <c r="D67">
-        <v>1259.989391187204</v>
+        <v>1263.881184517018</v>
       </c>
       <c r="E67">
-        <v>-25.9899999999999</v>
+        <v>-11.71599999999989</v>
       </c>
       <c r="F67">
-        <v>927.8100000000001</v>
+        <v>942.0840000000001</v>
       </c>
       <c r="G67">
         <v>256.4</v>
@@ -6781,28 +6781,28 @@
         <v>394.925</v>
       </c>
       <c r="M67">
-        <v>49.637835</v>
+        <v>50.401494</v>
       </c>
       <c r="N67">
-        <v>345.287165</v>
+        <v>344.5235059999999</v>
       </c>
       <c r="O67">
-        <v>120.85050775</v>
+        <v>120.5832271</v>
       </c>
       <c r="P67">
-        <v>224.43665725</v>
+        <v>223.9402789</v>
       </c>
       <c r="Q67">
-        <v>266.63665725</v>
+        <v>266.1402788999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1536077921574209</v>
+        <v>0.1562757938670087</v>
       </c>
       <c r="T67">
-        <v>1.568734735690036</v>
+        <v>1.60755741142575</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.956128626480183</v>
+        <v>7.835581223048665</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07608526991478295</v>
+        <v>0.07580406257446862</v>
       </c>
       <c r="C68">
-        <v>578.1971845170176</v>
+        <v>567.839093895373</v>
       </c>
       <c r="D68">
-        <v>1263.881184517018</v>
+        <v>1267.797093895373</v>
       </c>
       <c r="E68">
-        <v>-11.71599999999989</v>
+        <v>2.55800000000022</v>
       </c>
       <c r="F68">
-        <v>942.0840000000001</v>
+        <v>956.3580000000002</v>
       </c>
       <c r="G68">
         <v>256.4</v>
@@ -6863,28 +6863,28 @@
         <v>394.925</v>
       </c>
       <c r="M68">
-        <v>50.401494</v>
+        <v>51.16515300000001</v>
       </c>
       <c r="N68">
-        <v>344.5235059999999</v>
+        <v>343.7598469999999</v>
       </c>
       <c r="O68">
-        <v>120.5832271</v>
+        <v>120.31594645</v>
       </c>
       <c r="P68">
-        <v>223.9402789</v>
+        <v>223.44390055</v>
       </c>
       <c r="Q68">
-        <v>266.1402788999999</v>
+        <v>265.64390055</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1562757938670087</v>
+        <v>0.1591054926499049</v>
       </c>
       <c r="T68">
-        <v>1.60755741142575</v>
+        <v>1.648732976599992</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.835581223048665</v>
+        <v>7.718632249570325</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07580406257446862</v>
+        <v>0.07587645523415425</v>
       </c>
       <c r="C69">
-        <v>567.839093895373</v>
+        <v>552.5546836209513</v>
       </c>
       <c r="D69">
-        <v>1267.797093895373</v>
+        <v>1266.786683620951</v>
       </c>
       <c r="E69">
-        <v>2.55800000000022</v>
+        <v>16.83200000000022</v>
       </c>
       <c r="F69">
-        <v>956.3580000000002</v>
+        <v>970.6320000000002</v>
       </c>
       <c r="G69">
         <v>256.4</v>
@@ -6945,45 +6945,45 @@
         <v>394.925</v>
       </c>
       <c r="M69">
-        <v>51.16515300000001</v>
+        <v>52.70531760000001</v>
       </c>
       <c r="N69">
-        <v>343.7598469999999</v>
+        <v>342.2196824</v>
       </c>
       <c r="O69">
-        <v>120.31594645</v>
+        <v>119.77688884</v>
       </c>
       <c r="P69">
-        <v>223.44390055</v>
+        <v>222.44279356</v>
       </c>
       <c r="Q69">
-        <v>265.64390055</v>
+        <v>264.64279356</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1591054926499049</v>
+        <v>0.1621120476067321</v>
       </c>
       <c r="T69">
-        <v>1.648732976599992</v>
+        <v>1.692482014597624</v>
       </c>
       <c r="U69">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V69">
         <v>0.35</v>
       </c>
       <c r="W69">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y69">
-        <v>7.718632249570325</v>
+        <v>7.493076941443189</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07587645523415425</v>
+        <v>0.07560044789383989</v>
       </c>
       <c r="C70">
-        <v>552.5546836209513</v>
+        <v>542.1416787038954</v>
       </c>
       <c r="D70">
-        <v>1266.786683620951</v>
+        <v>1270.647678703896</v>
       </c>
       <c r="E70">
-        <v>16.83200000000022</v>
+        <v>31.10600000000022</v>
       </c>
       <c r="F70">
-        <v>970.6320000000002</v>
+        <v>984.9060000000002</v>
       </c>
       <c r="G70">
         <v>256.4</v>
@@ -7027,28 +7027,28 @@
         <v>394.925</v>
       </c>
       <c r="M70">
-        <v>52.70531760000001</v>
+        <v>53.48039580000001</v>
       </c>
       <c r="N70">
-        <v>342.2196824</v>
+        <v>341.4446042</v>
       </c>
       <c r="O70">
-        <v>119.77688884</v>
+        <v>119.50561147</v>
       </c>
       <c r="P70">
-        <v>222.44279356</v>
+        <v>221.93899273</v>
       </c>
       <c r="Q70">
-        <v>264.64279356</v>
+        <v>264.13899273</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1621120476067321</v>
+        <v>0.1653125738510965</v>
       </c>
       <c r="T70">
-        <v>1.692482014597624</v>
+        <v>1.739053571175749</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.493076941443189</v>
+        <v>7.384481623451259</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07560044789383989</v>
+        <v>0.07532444055352554</v>
       </c>
       <c r="C71">
-        <v>542.1416787038954</v>
+        <v>531.7522813247439</v>
       </c>
       <c r="D71">
-        <v>1270.647678703896</v>
+        <v>1274.532281324744</v>
       </c>
       <c r="E71">
-        <v>31.10600000000022</v>
+        <v>45.38000000000022</v>
       </c>
       <c r="F71">
-        <v>984.9060000000002</v>
+        <v>999.1800000000002</v>
       </c>
       <c r="G71">
         <v>256.4</v>
@@ -7109,28 +7109,28 @@
         <v>394.925</v>
       </c>
       <c r="M71">
-        <v>53.48039580000001</v>
+        <v>54.25547400000001</v>
       </c>
       <c r="N71">
-        <v>341.4446042</v>
+        <v>340.669526</v>
       </c>
       <c r="O71">
-        <v>119.50561147</v>
+        <v>119.2343341</v>
       </c>
       <c r="P71">
-        <v>221.93899273</v>
+        <v>221.4351919</v>
       </c>
       <c r="Q71">
-        <v>264.13899273</v>
+        <v>263.6351919</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1653125738510965</v>
+        <v>0.1687264685117518</v>
       </c>
       <c r="T71">
-        <v>1.739053571175749</v>
+        <v>1.788729898192415</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>7.384481623451259</v>
+        <v>7.278989028830527</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07532444055352554</v>
+        <v>0.0750484332132112</v>
       </c>
       <c r="C72">
-        <v>531.7522813247439</v>
+        <v>521.3867086651571</v>
       </c>
       <c r="D72">
-        <v>1274.532281324744</v>
+        <v>1278.440708665157</v>
       </c>
       <c r="E72">
-        <v>45.38000000000022</v>
+        <v>59.65400000000022</v>
       </c>
       <c r="F72">
-        <v>999.1800000000002</v>
+        <v>1013.454</v>
       </c>
       <c r="G72">
         <v>256.4</v>
@@ -7191,28 +7191,28 @@
         <v>394.925</v>
       </c>
       <c r="M72">
-        <v>54.25547400000001</v>
+        <v>55.03055220000001</v>
       </c>
       <c r="N72">
-        <v>340.669526</v>
+        <v>339.8944478</v>
       </c>
       <c r="O72">
-        <v>119.2343341</v>
+        <v>118.96305673</v>
       </c>
       <c r="P72">
-        <v>221.4351919</v>
+        <v>220.93139107</v>
       </c>
       <c r="Q72">
-        <v>263.6351919</v>
+        <v>263.1313910699999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1687264685117518</v>
+        <v>0.1723758041834869</v>
       </c>
       <c r="T72">
-        <v>1.788729898192415</v>
+        <v>1.841832178796438</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>7.278989028830527</v>
+        <v>7.176468056593477</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07504843321321118</v>
+        <v>0.07477242587289683</v>
       </c>
       <c r="C73">
-        <v>521.3867086651572</v>
+        <v>511.0451805789944</v>
       </c>
       <c r="D73">
-        <v>1278.440708665157</v>
+        <v>1282.373180578994</v>
       </c>
       <c r="E73">
-        <v>59.65400000000011</v>
+        <v>73.92800000000011</v>
       </c>
       <c r="F73">
-        <v>1013.454</v>
+        <v>1027.728</v>
       </c>
       <c r="G73">
         <v>256.4</v>
@@ -7273,28 +7273,28 @@
         <v>394.925</v>
       </c>
       <c r="M73">
-        <v>55.0305522</v>
+        <v>55.80563040000001</v>
       </c>
       <c r="N73">
-        <v>339.8944478</v>
+        <v>339.1193696</v>
       </c>
       <c r="O73">
-        <v>118.96305673</v>
+        <v>118.69177936</v>
       </c>
       <c r="P73">
-        <v>220.93139107</v>
+        <v>220.42759024</v>
       </c>
       <c r="Q73">
-        <v>263.1313910699999</v>
+        <v>262.62759024</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1723758041834868</v>
+        <v>0.1762858066889172</v>
       </c>
       <c r="T73">
-        <v>1.841832178796437</v>
+        <v>1.898727479443604</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>7.176468056593478</v>
+        <v>7.076794889140791</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07477242587289683</v>
+        <v>0.07449641853258246</v>
       </c>
       <c r="C74">
-        <v>511.0451805789944</v>
+        <v>500.7279196335326</v>
       </c>
       <c r="D74">
-        <v>1282.373180578994</v>
+        <v>1286.329919633533</v>
       </c>
       <c r="E74">
-        <v>73.92800000000011</v>
+        <v>88.202</v>
       </c>
       <c r="F74">
-        <v>1027.728</v>
+        <v>1042.002</v>
       </c>
       <c r="G74">
         <v>256.4</v>
@@ -7355,28 +7355,28 @@
         <v>394.925</v>
       </c>
       <c r="M74">
-        <v>55.80563040000001</v>
+        <v>56.5807086</v>
       </c>
       <c r="N74">
-        <v>339.1193696</v>
+        <v>338.3442914</v>
       </c>
       <c r="O74">
-        <v>118.69177936</v>
+        <v>118.42050199</v>
       </c>
       <c r="P74">
-        <v>220.42759024</v>
+        <v>219.92378941</v>
       </c>
       <c r="Q74">
-        <v>262.62759024</v>
+        <v>262.12378941</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1762858066889172</v>
+        <v>0.1804854390095647</v>
       </c>
       <c r="T74">
-        <v>1.898727479443604</v>
+        <v>1.959837246805375</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>7.076794889140791</v>
+        <v>6.979852493399137</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07449641853258246</v>
+        <v>0.07422041119226812</v>
       </c>
       <c r="C75">
-        <v>500.7279196335326</v>
+        <v>490.4351511514612</v>
       </c>
       <c r="D75">
-        <v>1286.329919633533</v>
+        <v>1290.311151151461</v>
       </c>
       <c r="E75">
-        <v>88.202</v>
+        <v>102.4760000000001</v>
       </c>
       <c r="F75">
-        <v>1042.002</v>
+        <v>1056.276</v>
       </c>
       <c r="G75">
         <v>256.4</v>
@@ -7437,28 +7437,28 @@
         <v>394.925</v>
       </c>
       <c r="M75">
-        <v>56.5807086</v>
+        <v>57.3557868</v>
       </c>
       <c r="N75">
-        <v>338.3442914</v>
+        <v>337.5692131999999</v>
       </c>
       <c r="O75">
-        <v>118.42050199</v>
+        <v>118.14922462</v>
       </c>
       <c r="P75">
-        <v>219.92378941</v>
+        <v>219.4199885799999</v>
       </c>
       <c r="Q75">
-        <v>262.12378941</v>
+        <v>261.6199885799999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1804854390095647</v>
+        <v>0.185008119970262</v>
       </c>
       <c r="T75">
-        <v>1.959837246805375</v>
+        <v>2.025647765502668</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.979852493399137</v>
+        <v>6.885530162407255</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07422041119226812</v>
+        <v>0.07394440385195376</v>
       </c>
       <c r="C76">
-        <v>490.4351511514612</v>
+        <v>480.1671032536519</v>
       </c>
       <c r="D76">
-        <v>1290.311151151461</v>
+        <v>1294.317103253652</v>
       </c>
       <c r="E76">
-        <v>102.4760000000001</v>
+        <v>116.7500000000002</v>
       </c>
       <c r="F76">
-        <v>1056.276</v>
+        <v>1070.55</v>
       </c>
       <c r="G76">
         <v>256.4</v>
@@ -7519,28 +7519,28 @@
         <v>394.925</v>
       </c>
       <c r="M76">
-        <v>57.3557868</v>
+        <v>58.13086500000001</v>
       </c>
       <c r="N76">
-        <v>337.5692131999999</v>
+        <v>336.7941349999999</v>
       </c>
       <c r="O76">
-        <v>118.14922462</v>
+        <v>117.87794725</v>
       </c>
       <c r="P76">
-        <v>219.4199885799999</v>
+        <v>218.9161877499999</v>
       </c>
       <c r="Q76">
-        <v>261.6199885799999</v>
+        <v>261.1161877499999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.185008119970262</v>
+        <v>0.189892615407815</v>
       </c>
       <c r="T76">
-        <v>2.025647765502668</v>
+        <v>2.096723125695744</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.885530162407255</v>
+        <v>6.793723093575157</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07394440385195376</v>
+        <v>0.07366839651163939</v>
       </c>
       <c r="C77">
-        <v>480.1671032536519</v>
+        <v>469.9240069027342</v>
       </c>
       <c r="D77">
-        <v>1294.317103253652</v>
+        <v>1298.348006902734</v>
       </c>
       <c r="E77">
-        <v>116.7500000000002</v>
+        <v>131.0240000000001</v>
       </c>
       <c r="F77">
-        <v>1070.55</v>
+        <v>1084.824</v>
       </c>
       <c r="G77">
         <v>256.4</v>
@@ -7601,28 +7601,28 @@
         <v>394.925</v>
       </c>
       <c r="M77">
-        <v>58.13086500000001</v>
+        <v>58.9059432</v>
       </c>
       <c r="N77">
-        <v>336.7941349999999</v>
+        <v>336.0190567999999</v>
       </c>
       <c r="O77">
-        <v>117.87794725</v>
+        <v>117.60666988</v>
       </c>
       <c r="P77">
-        <v>218.9161877499999</v>
+        <v>218.41238692</v>
       </c>
       <c r="Q77">
-        <v>261.1161877499999</v>
+        <v>260.6123869199999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.189892615407815</v>
+        <v>0.1951841521318309</v>
       </c>
       <c r="T77">
-        <v>2.096723125695744</v>
+        <v>2.173721432571577</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.793723093575157</v>
+        <v>6.704332000238644</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07366839651163939</v>
+        <v>0.07339238917132504</v>
       </c>
       <c r="C78">
-        <v>469.9240069027342</v>
+        <v>459.70609594748</v>
       </c>
       <c r="D78">
-        <v>1298.348006902734</v>
+        <v>1302.40409594748</v>
       </c>
       <c r="E78">
-        <v>131.0240000000001</v>
+        <v>145.2980000000002</v>
       </c>
       <c r="F78">
-        <v>1084.824</v>
+        <v>1099.098</v>
       </c>
       <c r="G78">
         <v>256.4</v>
@@ -7683,28 +7683,28 @@
         <v>394.925</v>
       </c>
       <c r="M78">
-        <v>58.9059432</v>
+        <v>59.68102140000001</v>
       </c>
       <c r="N78">
-        <v>336.0190567999999</v>
+        <v>335.2439785999999</v>
       </c>
       <c r="O78">
-        <v>117.60666988</v>
+        <v>117.33539251</v>
       </c>
       <c r="P78">
-        <v>218.41238692</v>
+        <v>217.90858609</v>
       </c>
       <c r="Q78">
-        <v>260.6123869199999</v>
+        <v>260.10858609</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1951841521318309</v>
+        <v>0.2009358224840219</v>
       </c>
       <c r="T78">
-        <v>2.173721432571577</v>
+        <v>2.257415244393134</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.704332000238644</v>
+        <v>6.617262753482296</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07339238917132504</v>
+        <v>0.07311638183101068</v>
       </c>
       <c r="C79">
-        <v>459.70609594748</v>
+        <v>449.5136071680297</v>
       </c>
       <c r="D79">
-        <v>1302.40409594748</v>
+        <v>1306.48560716803</v>
       </c>
       <c r="E79">
-        <v>145.2980000000002</v>
+        <v>159.5720000000001</v>
       </c>
       <c r="F79">
-        <v>1099.098</v>
+        <v>1113.372</v>
       </c>
       <c r="G79">
         <v>256.4</v>
@@ -7765,28 +7765,28 @@
         <v>394.925</v>
       </c>
       <c r="M79">
-        <v>59.68102140000001</v>
+        <v>60.4560996</v>
       </c>
       <c r="N79">
-        <v>335.2439785999999</v>
+        <v>334.4689003999999</v>
       </c>
       <c r="O79">
-        <v>117.33539251</v>
+        <v>117.06411514</v>
       </c>
       <c r="P79">
-        <v>217.90858609</v>
+        <v>217.40478526</v>
       </c>
       <c r="Q79">
-        <v>260.10858609</v>
+        <v>259.60478526</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2009358224840219</v>
+        <v>0.2072103719591395</v>
       </c>
       <c r="T79">
-        <v>2.257415244393134</v>
+        <v>2.348717584562105</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.617262753482296</v>
+        <v>6.532426051514576</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07311638183101068</v>
+        <v>0.07284037449069633</v>
       </c>
       <c r="C80">
-        <v>449.5136071680297</v>
+        <v>439.3467803219687</v>
       </c>
       <c r="D80">
-        <v>1306.48560716803</v>
+        <v>1310.592780321969</v>
       </c>
       <c r="E80">
-        <v>159.5720000000001</v>
+        <v>173.8460000000002</v>
       </c>
       <c r="F80">
-        <v>1113.372</v>
+        <v>1127.646</v>
       </c>
       <c r="G80">
         <v>256.4</v>
@@ -7847,28 +7847,28 @@
         <v>394.925</v>
       </c>
       <c r="M80">
-        <v>60.4560996</v>
+        <v>61.23117780000001</v>
       </c>
       <c r="N80">
-        <v>334.4689003999999</v>
+        <v>333.6938221999999</v>
       </c>
       <c r="O80">
-        <v>117.06411514</v>
+        <v>116.79283777</v>
       </c>
       <c r="P80">
-        <v>217.40478526</v>
+        <v>216.90098443</v>
       </c>
       <c r="Q80">
-        <v>259.60478526</v>
+        <v>259.1009844299999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2072103719591395</v>
+        <v>0.2140824975747445</v>
       </c>
       <c r="T80">
-        <v>2.348717584562105</v>
+        <v>2.44871538569955</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>6.532426051514576</v>
+        <v>6.449737114153631</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07284037449069633</v>
+        <v>0.07256436715038196</v>
       </c>
       <c r="C81">
-        <v>439.3467803219687</v>
+        <v>429.2058581912747</v>
       </c>
       <c r="D81">
-        <v>1310.592780321969</v>
+        <v>1314.725858191275</v>
       </c>
       <c r="E81">
-        <v>173.8460000000002</v>
+        <v>188.1200000000001</v>
       </c>
       <c r="F81">
-        <v>1127.646</v>
+        <v>1141.92</v>
       </c>
       <c r="G81">
         <v>256.4</v>
@@ -7929,28 +7929,28 @@
         <v>394.925</v>
       </c>
       <c r="M81">
-        <v>61.23117780000001</v>
+        <v>62.00625600000001</v>
       </c>
       <c r="N81">
-        <v>333.6938221999999</v>
+        <v>332.9187439999999</v>
       </c>
       <c r="O81">
-        <v>116.79283777</v>
+        <v>116.5215604</v>
       </c>
       <c r="P81">
-        <v>216.90098443</v>
+        <v>216.3971836</v>
       </c>
       <c r="Q81">
-        <v>259.1009844299999</v>
+        <v>258.5971836</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2140824975747445</v>
+        <v>0.2216418357519099</v>
       </c>
       <c r="T81">
-        <v>2.44871538569955</v>
+        <v>2.558712966950739</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>6.449737114153631</v>
+        <v>6.369115400226711</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07256436715038196</v>
+        <v>0.07228835981006762</v>
       </c>
       <c r="C82">
-        <v>429.2058581912747</v>
+        <v>419.0910866301567</v>
       </c>
       <c r="D82">
-        <v>1314.725858191275</v>
+        <v>1318.885086630157</v>
       </c>
       <c r="E82">
-        <v>188.1200000000001</v>
+        <v>202.3940000000002</v>
       </c>
       <c r="F82">
-        <v>1141.92</v>
+        <v>1156.194</v>
       </c>
       <c r="G82">
         <v>256.4</v>
@@ -8011,28 +8011,28 @@
         <v>394.925</v>
       </c>
       <c r="M82">
-        <v>62.00625600000001</v>
+        <v>62.78133420000001</v>
       </c>
       <c r="N82">
-        <v>332.9187439999999</v>
+        <v>332.1436658</v>
       </c>
       <c r="O82">
-        <v>116.5215604</v>
+        <v>116.25028303</v>
       </c>
       <c r="P82">
-        <v>216.3971836</v>
+        <v>215.89338277</v>
       </c>
       <c r="Q82">
-        <v>258.5971836</v>
+        <v>258.0933827699999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2216418357519099</v>
+        <v>0.229996893737198</v>
       </c>
       <c r="T82">
-        <v>2.558712966950739</v>
+        <v>2.680289240965211</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>6.369115400226711</v>
+        <v>6.290484345902924</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07228835981006762</v>
+        <v>0.07201235246975327</v>
       </c>
       <c r="C83">
-        <v>419.0910866301567</v>
+        <v>409.0027146138066</v>
       </c>
       <c r="D83">
-        <v>1318.885086630157</v>
+        <v>1323.070714613807</v>
       </c>
       <c r="E83">
-        <v>202.3940000000002</v>
+        <v>216.6680000000001</v>
       </c>
       <c r="F83">
-        <v>1156.194</v>
+        <v>1170.468</v>
       </c>
       <c r="G83">
         <v>256.4</v>
@@ -8093,28 +8093,28 @@
         <v>394.925</v>
       </c>
       <c r="M83">
-        <v>62.78133420000001</v>
+        <v>63.55641240000001</v>
       </c>
       <c r="N83">
-        <v>332.1436658</v>
+        <v>331.3685876</v>
       </c>
       <c r="O83">
-        <v>116.25028303</v>
+        <v>115.97900566</v>
       </c>
       <c r="P83">
-        <v>215.89338277</v>
+        <v>215.38958194</v>
       </c>
       <c r="Q83">
-        <v>258.0933827699999</v>
+        <v>257.58958194</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.229996893737198</v>
+        <v>0.2392802914986293</v>
       </c>
       <c r="T83">
-        <v>2.680289240965211</v>
+        <v>2.815373989870181</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>6.290484345902924</v>
+        <v>6.213771122172401</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07201235246975327</v>
+        <v>0.07173634512943891</v>
       </c>
       <c r="C84">
-        <v>409.0027146138066</v>
+        <v>398.9409942880802</v>
       </c>
       <c r="D84">
-        <v>1323.070714613807</v>
+        <v>1327.282994288081</v>
       </c>
       <c r="E84">
-        <v>216.6680000000001</v>
+        <v>230.9420000000002</v>
       </c>
       <c r="F84">
-        <v>1170.468</v>
+        <v>1184.742</v>
       </c>
       <c r="G84">
         <v>256.4</v>
@@ -8175,28 +8175,28 @@
         <v>394.925</v>
       </c>
       <c r="M84">
-        <v>63.55641240000001</v>
+        <v>64.33149060000001</v>
       </c>
       <c r="N84">
-        <v>331.3685876</v>
+        <v>330.5935094</v>
       </c>
       <c r="O84">
-        <v>115.97900566</v>
+        <v>115.70772829</v>
       </c>
       <c r="P84">
-        <v>215.38958194</v>
+        <v>214.88578111</v>
       </c>
       <c r="Q84">
-        <v>257.58958194</v>
+        <v>257.08578111</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2392802914986293</v>
+        <v>0.2496558537025819</v>
       </c>
       <c r="T84">
-        <v>2.815373989870181</v>
+        <v>2.966351062175735</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>6.213771122172401</v>
+        <v>6.138906409857071</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07173634512943891</v>
+        <v>0.07200633778912455</v>
       </c>
       <c r="C85">
-        <v>398.9409942880802</v>
+        <v>380.5462225374242</v>
       </c>
       <c r="D85">
-        <v>1327.282994288081</v>
+        <v>1323.162222537424</v>
       </c>
       <c r="E85">
-        <v>230.9420000000002</v>
+        <v>245.2160000000003</v>
       </c>
       <c r="F85">
-        <v>1184.742</v>
+        <v>1199.016</v>
       </c>
       <c r="G85">
         <v>256.4</v>
@@ -8257,45 +8257,45 @@
         <v>394.925</v>
       </c>
       <c r="M85">
-        <v>64.33149060000001</v>
+        <v>66.30558480000002</v>
       </c>
       <c r="N85">
-        <v>330.5935094</v>
+        <v>328.6194151999999</v>
       </c>
       <c r="O85">
-        <v>115.70772829</v>
+        <v>115.01679532</v>
       </c>
       <c r="P85">
-        <v>214.88578111</v>
+        <v>213.60261988</v>
       </c>
       <c r="Q85">
-        <v>257.08578111</v>
+        <v>255.80261988</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2496558537025819</v>
+        <v>0.2613283611820285</v>
       </c>
       <c r="T85">
-        <v>2.966351062175735</v>
+        <v>3.136200268519484</v>
       </c>
       <c r="U85">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V85">
         <v>0.35</v>
       </c>
       <c r="W85">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y85">
-        <v>6.138906409857071</v>
+        <v>5.956134783988812</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07200633778912455</v>
+        <v>0.0717368304488102</v>
       </c>
       <c r="C86">
-        <v>380.5462225374245</v>
+        <v>370.385564058467</v>
       </c>
       <c r="D86">
-        <v>1323.162222537424</v>
+        <v>1327.275564058467</v>
       </c>
       <c r="E86">
-        <v>245.2160000000001</v>
+        <v>259.49</v>
       </c>
       <c r="F86">
-        <v>1199.016</v>
+        <v>1213.29</v>
       </c>
       <c r="G86">
         <v>256.4</v>
@@ -8339,28 +8339,28 @@
         <v>394.925</v>
       </c>
       <c r="M86">
-        <v>66.30558480000001</v>
+        <v>67.094937</v>
       </c>
       <c r="N86">
-        <v>328.6194151999999</v>
+        <v>327.8300629999999</v>
       </c>
       <c r="O86">
-        <v>115.01679532</v>
+        <v>114.74052205</v>
       </c>
       <c r="P86">
-        <v>213.60261988</v>
+        <v>213.08954095</v>
       </c>
       <c r="Q86">
-        <v>255.80261988</v>
+        <v>255.2895409499999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2613283611820283</v>
+        <v>0.2745572029920679</v>
       </c>
       <c r="T86">
-        <v>3.136200268519481</v>
+        <v>3.328696035709063</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.956134783988813</v>
+        <v>5.886062610059533</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0717368304488102</v>
+        <v>0.07146732310849584</v>
       </c>
       <c r="C87">
-        <v>370.385564058467</v>
+        <v>360.2505597894667</v>
       </c>
       <c r="D87">
-        <v>1327.275564058467</v>
+        <v>1331.414559789467</v>
       </c>
       <c r="E87">
-        <v>259.49</v>
+        <v>273.7640000000001</v>
       </c>
       <c r="F87">
-        <v>1213.29</v>
+        <v>1227.564</v>
       </c>
       <c r="G87">
         <v>256.4</v>
@@ -8421,28 +8421,28 @@
         <v>394.925</v>
       </c>
       <c r="M87">
-        <v>67.094937</v>
+        <v>67.88428920000001</v>
       </c>
       <c r="N87">
-        <v>327.8300629999999</v>
+        <v>327.0407107999999</v>
       </c>
       <c r="O87">
-        <v>114.74052205</v>
+        <v>114.46424878</v>
       </c>
       <c r="P87">
-        <v>213.08954095</v>
+        <v>212.57646202</v>
       </c>
       <c r="Q87">
-        <v>255.2895409499999</v>
+        <v>254.7764620199999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2745572029920679</v>
+        <v>0.2896758793463988</v>
       </c>
       <c r="T87">
-        <v>3.328696035709063</v>
+        <v>3.548691198211441</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.886062610059533</v>
+        <v>5.817620021570468</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07146732310849584</v>
+        <v>0.07119781576818147</v>
       </c>
       <c r="C88">
-        <v>360.2505597894667</v>
+        <v>350.1414504825918</v>
       </c>
       <c r="D88">
-        <v>1331.414559789467</v>
+        <v>1335.579450482592</v>
       </c>
       <c r="E88">
-        <v>273.7640000000001</v>
+        <v>288.038</v>
       </c>
       <c r="F88">
-        <v>1227.564</v>
+        <v>1241.838</v>
       </c>
       <c r="G88">
         <v>256.4</v>
@@ -8503,28 +8503,28 @@
         <v>394.925</v>
       </c>
       <c r="M88">
-        <v>67.88428920000001</v>
+        <v>68.67364139999999</v>
       </c>
       <c r="N88">
-        <v>327.0407107999999</v>
+        <v>326.2513585999999</v>
       </c>
       <c r="O88">
-        <v>114.46424878</v>
+        <v>114.18797551</v>
       </c>
       <c r="P88">
-        <v>212.57646202</v>
+        <v>212.06338309</v>
       </c>
       <c r="Q88">
-        <v>254.7764620199999</v>
+        <v>254.26338309</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2896758793463988</v>
+        <v>0.3071205059090882</v>
       </c>
       <c r="T88">
-        <v>3.548691198211441</v>
+        <v>3.80253177032957</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.817620021570468</v>
+        <v>5.750750825920234</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07119781576818147</v>
+        <v>0.07092830842786713</v>
       </c>
       <c r="C89">
-        <v>350.1414504825918</v>
+        <v>340.0584799119156</v>
       </c>
       <c r="D89">
-        <v>1335.579450482592</v>
+        <v>1339.770479911916</v>
       </c>
       <c r="E89">
-        <v>288.038</v>
+        <v>302.3120000000001</v>
       </c>
       <c r="F89">
-        <v>1241.838</v>
+        <v>1256.112</v>
       </c>
       <c r="G89">
         <v>256.4</v>
@@ -8585,28 +8585,28 @@
         <v>394.925</v>
       </c>
       <c r="M89">
-        <v>68.67364139999999</v>
+        <v>69.4629936</v>
       </c>
       <c r="N89">
-        <v>326.2513585999999</v>
+        <v>325.4620064</v>
       </c>
       <c r="O89">
-        <v>114.18797551</v>
+        <v>113.91170224</v>
       </c>
       <c r="P89">
-        <v>212.06338309</v>
+        <v>211.55030416</v>
       </c>
       <c r="Q89">
-        <v>254.26338309</v>
+        <v>253.75030416</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3071205059090882</v>
+        <v>0.327472570232226</v>
       </c>
       <c r="T89">
-        <v>3.80253177032957</v>
+        <v>4.098679104467387</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.750750825920234</v>
+        <v>5.685401384716594</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07092830842786713</v>
+        <v>0.07065880108755276</v>
       </c>
       <c r="C90">
-        <v>340.0584799119156</v>
+        <v>330.0018949209841</v>
       </c>
       <c r="D90">
-        <v>1339.770479911916</v>
+        <v>1343.987894920984</v>
       </c>
       <c r="E90">
-        <v>302.3120000000001</v>
+        <v>316.5860000000002</v>
       </c>
       <c r="F90">
-        <v>1256.112</v>
+        <v>1270.386</v>
       </c>
       <c r="G90">
         <v>256.4</v>
@@ -8667,28 +8667,28 @@
         <v>394.925</v>
       </c>
       <c r="M90">
-        <v>69.4629936</v>
+        <v>70.25234580000001</v>
       </c>
       <c r="N90">
-        <v>325.4620064</v>
+        <v>324.6726542</v>
       </c>
       <c r="O90">
-        <v>113.91170224</v>
+        <v>113.63542897</v>
       </c>
       <c r="P90">
-        <v>211.55030416</v>
+        <v>211.03722523</v>
       </c>
       <c r="Q90">
-        <v>253.75030416</v>
+        <v>253.23722523</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.327472570232226</v>
+        <v>0.3515250098868433</v>
       </c>
       <c r="T90">
-        <v>4.098679104467387</v>
+        <v>4.448671408448444</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.685401384716594</v>
+        <v>5.621520470281576</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07065880108755276</v>
+        <v>0.0703892937472384</v>
       </c>
       <c r="C91">
-        <v>330.0018949209841</v>
+        <v>319.9719454712774</v>
       </c>
       <c r="D91">
-        <v>1343.987894920984</v>
+        <v>1348.231945471277</v>
       </c>
       <c r="E91">
-        <v>316.5860000000002</v>
+        <v>330.8600000000001</v>
       </c>
       <c r="F91">
-        <v>1270.386</v>
+        <v>1284.66</v>
       </c>
       <c r="G91">
         <v>256.4</v>
@@ -8749,28 +8749,28 @@
         <v>394.925</v>
       </c>
       <c r="M91">
-        <v>70.25234580000001</v>
+        <v>71.04169800000001</v>
       </c>
       <c r="N91">
-        <v>324.6726542</v>
+        <v>323.883302</v>
       </c>
       <c r="O91">
-        <v>113.63542897</v>
+        <v>113.3591557</v>
       </c>
       <c r="P91">
-        <v>211.03722523</v>
+        <v>210.5241463</v>
       </c>
       <c r="Q91">
-        <v>253.23722523</v>
+        <v>252.7241463</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3515250098868433</v>
+        <v>0.3803879374723841</v>
       </c>
       <c r="T91">
-        <v>4.448671408448444</v>
+        <v>4.868662173225712</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.621520470281576</v>
+        <v>5.559059131722892</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0703892937472384</v>
+        <v>0.07011978640692405</v>
       </c>
       <c r="C92">
-        <v>319.9719454712774</v>
+        <v>309.9688846915933</v>
       </c>
       <c r="D92">
-        <v>1348.231945471277</v>
+        <v>1352.502884691594</v>
       </c>
       <c r="E92">
-        <v>330.8600000000001</v>
+        <v>345.1340000000002</v>
       </c>
       <c r="F92">
-        <v>1284.66</v>
+        <v>1298.934</v>
       </c>
       <c r="G92">
         <v>256.4</v>
@@ -8831,28 +8831,28 @@
         <v>394.925</v>
       </c>
       <c r="M92">
-        <v>71.04169800000001</v>
+        <v>71.83105020000001</v>
       </c>
       <c r="N92">
-        <v>323.883302</v>
+        <v>323.0939498</v>
       </c>
       <c r="O92">
-        <v>113.3591557</v>
+        <v>113.08288243</v>
       </c>
       <c r="P92">
-        <v>210.5241463</v>
+        <v>210.01106737</v>
       </c>
       <c r="Q92">
-        <v>252.7241463</v>
+        <v>252.21106737</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3803879374723841</v>
+        <v>0.4156648489658229</v>
       </c>
       <c r="T92">
-        <v>4.868662173225712</v>
+        <v>5.381984219064596</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.559059131722892</v>
+        <v>5.497970569835828</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07011978640692405</v>
+        <v>0.06985027906660971</v>
       </c>
       <c r="C93">
-        <v>309.9688846915933</v>
+        <v>299.9929689283776</v>
       </c>
       <c r="D93">
-        <v>1352.502884691594</v>
+        <v>1356.800968928378</v>
       </c>
       <c r="E93">
-        <v>345.1340000000002</v>
+        <v>359.4080000000001</v>
       </c>
       <c r="F93">
-        <v>1298.934</v>
+        <v>1313.208</v>
       </c>
       <c r="G93">
         <v>256.4</v>
@@ -8913,28 +8913,28 @@
         <v>394.925</v>
       </c>
       <c r="M93">
-        <v>71.83105020000001</v>
+        <v>72.6204024</v>
       </c>
       <c r="N93">
-        <v>323.0939498</v>
+        <v>322.3045976</v>
       </c>
       <c r="O93">
-        <v>113.08288243</v>
+        <v>112.80660916</v>
       </c>
       <c r="P93">
-        <v>210.01106737</v>
+        <v>209.49798844</v>
       </c>
       <c r="Q93">
-        <v>252.21106737</v>
+        <v>251.69798844</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4156648489658229</v>
+        <v>0.4597609883326214</v>
       </c>
       <c r="T93">
-        <v>5.381984219064596</v>
+        <v>6.023636776363201</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.497970569835828</v>
+        <v>5.438210020163699</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.06985027906660971</v>
+        <v>0.06958077172629532</v>
       </c>
       <c r="C94">
-        <v>299.9929689283776</v>
+        <v>290.0444577970113</v>
       </c>
       <c r="D94">
-        <v>1356.800968928378</v>
+        <v>1361.126457797011</v>
       </c>
       <c r="E94">
-        <v>359.4080000000001</v>
+        <v>373.6820000000002</v>
       </c>
       <c r="F94">
-        <v>1313.208</v>
+        <v>1327.482</v>
       </c>
       <c r="G94">
         <v>256.4</v>
@@ -8995,28 +8995,28 @@
         <v>394.925</v>
       </c>
       <c r="M94">
-        <v>72.6204024</v>
+        <v>73.40975460000001</v>
       </c>
       <c r="N94">
-        <v>322.3045976</v>
+        <v>321.5152453999999</v>
       </c>
       <c r="O94">
-        <v>112.80660916</v>
+        <v>112.53033589</v>
       </c>
       <c r="P94">
-        <v>209.49798844</v>
+        <v>208.98490951</v>
       </c>
       <c r="Q94">
-        <v>251.69798844</v>
+        <v>251.18490951</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4597609883326214</v>
+        <v>0.5164560246613621</v>
       </c>
       <c r="T94">
-        <v>6.023636776363201</v>
+        <v>6.84861863574712</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.438210020163699</v>
+        <v>5.379734643602798</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.06958077172629532</v>
+        <v>0.06931126438598098</v>
       </c>
       <c r="C95">
-        <v>290.0444577970113</v>
+        <v>280.123614234082</v>
       </c>
       <c r="D95">
-        <v>1361.126457797011</v>
+        <v>1365.479614234082</v>
       </c>
       <c r="E95">
-        <v>373.6820000000002</v>
+        <v>387.9560000000001</v>
       </c>
       <c r="F95">
-        <v>1327.482</v>
+        <v>1341.756</v>
       </c>
       <c r="G95">
         <v>256.4</v>
@@ -9077,28 +9077,28 @@
         <v>394.925</v>
       </c>
       <c r="M95">
-        <v>73.40975460000001</v>
+        <v>74.19910680000001</v>
       </c>
       <c r="N95">
-        <v>321.5152453999999</v>
+        <v>320.7258932</v>
       </c>
       <c r="O95">
-        <v>112.53033589</v>
+        <v>112.25406262</v>
       </c>
       <c r="P95">
-        <v>208.98490951</v>
+        <v>208.47183058</v>
       </c>
       <c r="Q95">
-        <v>251.18490951</v>
+        <v>250.67183058</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5164560246613621</v>
+        <v>0.5920494064330167</v>
       </c>
       <c r="T95">
-        <v>6.84861863574712</v>
+        <v>7.948594448259016</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.379734643602798</v>
+        <v>5.322503423990003</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.06931126438598098</v>
+        <v>0.06904175704566662</v>
       </c>
       <c r="C96">
-        <v>280.123614234082</v>
+        <v>270.2307045506695</v>
       </c>
       <c r="D96">
-        <v>1365.479614234082</v>
+        <v>1369.86070455067</v>
       </c>
       <c r="E96">
-        <v>387.9560000000001</v>
+        <v>402.2300000000002</v>
       </c>
       <c r="F96">
-        <v>1341.756</v>
+        <v>1356.03</v>
       </c>
       <c r="G96">
         <v>256.4</v>
@@ -9159,28 +9159,28 @@
         <v>394.925</v>
       </c>
       <c r="M96">
-        <v>74.19910680000001</v>
+        <v>74.98845900000002</v>
       </c>
       <c r="N96">
-        <v>320.7258932</v>
+        <v>319.9365409999999</v>
       </c>
       <c r="O96">
-        <v>112.25406262</v>
+        <v>111.97778935</v>
       </c>
       <c r="P96">
-        <v>208.47183058</v>
+        <v>207.95875165</v>
       </c>
       <c r="Q96">
-        <v>250.67183058</v>
+        <v>250.1587516499999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5920494064330167</v>
+        <v>0.6978801409133333</v>
       </c>
       <c r="T96">
-        <v>7.948594448259016</v>
+        <v>9.488560585775669</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.322503423990003</v>
+        <v>5.266477072158528</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.06904175704566662</v>
+        <v>0.06877224970535226</v>
       </c>
       <c r="C97">
-        <v>270.2307045506695</v>
+        <v>260.3659984866495</v>
       </c>
       <c r="D97">
-        <v>1369.86070455067</v>
+        <v>1374.26999848665</v>
       </c>
       <c r="E97">
-        <v>402.2300000000002</v>
+        <v>416.5040000000001</v>
       </c>
       <c r="F97">
-        <v>1356.03</v>
+        <v>1370.304</v>
       </c>
       <c r="G97">
         <v>256.4</v>
@@ -9241,28 +9241,28 @@
         <v>394.925</v>
       </c>
       <c r="M97">
-        <v>74.98845900000002</v>
+        <v>75.7778112</v>
       </c>
       <c r="N97">
-        <v>319.9365409999999</v>
+        <v>319.1471888</v>
       </c>
       <c r="O97">
-        <v>111.97778935</v>
+        <v>111.70151608</v>
       </c>
       <c r="P97">
-        <v>207.95875165</v>
+        <v>207.44567272</v>
       </c>
       <c r="Q97">
-        <v>250.1587516499999</v>
+        <v>249.64567272</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6978801409133333</v>
+        <v>0.8566262426338079</v>
       </c>
       <c r="T97">
-        <v>9.488560585775669</v>
+        <v>11.79850979205065</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.266477072158528</v>
+        <v>5.211617935990212</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.06877224970535227</v>
+        <v>0.06850274236503792</v>
       </c>
       <c r="C98">
-        <v>260.3659984866495</v>
+        <v>250.5297692660565</v>
       </c>
       <c r="D98">
-        <v>1374.269998486649</v>
+        <v>1378.707769266056</v>
       </c>
       <c r="E98">
-        <v>416.5040000000001</v>
+        <v>430.778</v>
       </c>
       <c r="F98">
-        <v>1370.304</v>
+        <v>1384.578</v>
       </c>
       <c r="G98">
         <v>256.4</v>
@@ -9323,28 +9323,28 @@
         <v>394.925</v>
       </c>
       <c r="M98">
-        <v>75.7778112</v>
+        <v>76.5671634</v>
       </c>
       <c r="N98">
-        <v>319.1471888</v>
+        <v>318.3578365999999</v>
       </c>
       <c r="O98">
-        <v>111.70151608</v>
+        <v>111.42524281</v>
       </c>
       <c r="P98">
-        <v>207.44567272</v>
+        <v>206.9325937899999</v>
       </c>
       <c r="Q98">
-        <v>249.64567272</v>
+        <v>249.1325937899999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8566262426338059</v>
+        <v>1.121203078834596</v>
       </c>
       <c r="T98">
-        <v>11.79850979205062</v>
+        <v>15.64842513584224</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.211617935990212</v>
+        <v>5.157889916031549</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.06850274236503792</v>
+        <v>0.06823323502472356</v>
       </c>
       <c r="C99">
-        <v>250.5297692660565</v>
+        <v>240.722293653522</v>
       </c>
       <c r="D99">
-        <v>1378.707769266056</v>
+        <v>1383.174293653522</v>
       </c>
       <c r="E99">
-        <v>430.778</v>
+        <v>445.0520000000001</v>
       </c>
       <c r="F99">
-        <v>1384.578</v>
+        <v>1398.852</v>
       </c>
       <c r="G99">
         <v>256.4</v>
@@ -9405,28 +9405,28 @@
         <v>394.925</v>
       </c>
       <c r="M99">
-        <v>76.5671634</v>
+        <v>77.35651560000001</v>
       </c>
       <c r="N99">
-        <v>318.3578365999999</v>
+        <v>317.5684843999999</v>
       </c>
       <c r="O99">
-        <v>111.42524281</v>
+        <v>111.14896954</v>
       </c>
       <c r="P99">
-        <v>206.9325937899999</v>
+        <v>206.41951486</v>
       </c>
       <c r="Q99">
-        <v>249.1325937899999</v>
+        <v>248.61951486</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.121203078834596</v>
+        <v>1.650356751236176</v>
       </c>
       <c r="T99">
-        <v>15.64842513584224</v>
+        <v>23.34825582342547</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.157889916031549</v>
+        <v>5.105258386276125</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.06823323502472356</v>
+        <v>0.0679637276844092</v>
       </c>
       <c r="C100">
-        <v>240.722293653522</v>
+        <v>230.9438520118108</v>
       </c>
       <c r="D100">
-        <v>1383.174293653522</v>
+        <v>1387.669852011811</v>
       </c>
       <c r="E100">
-        <v>445.0520000000001</v>
+        <v>459.326</v>
       </c>
       <c r="F100">
-        <v>1398.852</v>
+        <v>1413.126</v>
       </c>
       <c r="G100">
         <v>256.4</v>
@@ -9487,28 +9487,28 @@
         <v>394.925</v>
       </c>
       <c r="M100">
-        <v>77.35651560000001</v>
+        <v>78.1458678</v>
       </c>
       <c r="N100">
-        <v>317.5684843999999</v>
+        <v>316.7791321999999</v>
       </c>
       <c r="O100">
-        <v>111.14896954</v>
+        <v>110.87269627</v>
       </c>
       <c r="P100">
-        <v>206.41951486</v>
+        <v>205.90643593</v>
       </c>
       <c r="Q100">
-        <v>248.61951486</v>
+        <v>248.1064359299999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.650356751236176</v>
+        <v>3.237817768440916</v>
       </c>
       <c r="T100">
-        <v>23.34825582342547</v>
+        <v>46.44774788617518</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.105258386276125</v>
+        <v>5.053690119748084</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.0679637276844092</v>
-      </c>
-      <c r="C101">
-        <v>230.9438520118108</v>
-      </c>
-      <c r="D101">
-        <v>1387.669852011811</v>
-      </c>
-      <c r="E101">
-        <v>459.326</v>
-      </c>
-      <c r="F101">
-        <v>1413.126</v>
-      </c>
-      <c r="G101">
-        <v>256.4</v>
-      </c>
-      <c r="H101">
-        <v>473.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>437.1249999999999</v>
-      </c>
-      <c r="K101">
-        <v>42.19999999999999</v>
-      </c>
-      <c r="L101">
-        <v>394.925</v>
-      </c>
-      <c r="M101">
-        <v>78.1458678</v>
-      </c>
-      <c r="N101">
-        <v>316.7791321999999</v>
-      </c>
-      <c r="O101">
-        <v>110.87269627</v>
-      </c>
-      <c r="P101">
-        <v>205.90643593</v>
-      </c>
-      <c r="Q101">
-        <v>248.1064359299999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.237817768440916</v>
-      </c>
-      <c r="T101">
-        <v>46.44774788617518</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.035945</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.053690119748084</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
